--- a/Indicator_4/Real_data/Blue_Shark_NAtl.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_NAtl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BDC557-4317-4F66-8D22-8B96044AD832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AB8CB0-0A53-4770-98CC-D819B8557402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>Parameter</t>
   </si>
@@ -44,13 +44,10 @@
     <t>Blue_Shark_NAtl</t>
   </si>
   <si>
-    <t>Genus specius</t>
-  </si>
-  <si>
-    <t>Billfish</t>
-  </si>
-  <si>
-    <t>North Atlantic</t>
+    <t>E.g. 'Swordfish_Natl'</t>
+  </si>
+  <si>
+    <t>Stock</t>
   </si>
   <si>
     <t>max_age</t>
@@ -65,9 +62,6 @@
     <t>Life history</t>
   </si>
   <si>
-    <t>Stock</t>
-  </si>
-  <si>
     <t>K</t>
   </si>
   <si>
@@ -77,15 +71,27 @@
     <t>von Bertalannfy K</t>
   </si>
   <si>
+    <t>Linf</t>
+  </si>
+  <si>
+    <t>0.576</t>
+  </si>
+  <si>
+    <t>von Bertalannfy L-infinity (asymptotic length)</t>
+  </si>
+  <si>
     <t>L50_Linf</t>
   </si>
   <si>
-    <t>0.576</t>
+    <t>337.3</t>
   </si>
   <si>
     <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
   </si>
   <si>
+    <t>Total_L5_L50</t>
+  </si>
+  <si>
     <t>0.394</t>
   </si>
   <si>
@@ -98,12 +104,18 @@
     <t>All fleets combined</t>
   </si>
   <si>
+    <t>Total_LFS_L50</t>
+  </si>
+  <si>
     <t>0.881</t>
   </si>
   <si>
     <t>Length at full selection relative to length at 50% maturity</t>
   </si>
   <si>
+    <t>Total_VML</t>
+  </si>
+  <si>
     <t>0.468</t>
   </si>
   <si>
@@ -173,36 +185,6 @@
     <t>0.999</t>
   </si>
   <si>
-    <t>All_ML_Linf</t>
-  </si>
-  <si>
-    <t>0.471</t>
-  </si>
-  <si>
-    <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-  </si>
-  <si>
-    <t>Fleet catch-length</t>
-  </si>
-  <si>
-    <t>Fleet_1_ML_Linf</t>
-  </si>
-  <si>
-    <t>0.455</t>
-  </si>
-  <si>
-    <t>Fleet_2_ML_Linf</t>
-  </si>
-  <si>
-    <t>0.601</t>
-  </si>
-  <si>
-    <t>Fleet_3_ML_Linf</t>
-  </si>
-  <si>
-    <t>0.487</t>
-  </si>
-  <si>
     <t>Fleet_1_CF</t>
   </si>
   <si>
@@ -306,15 +288,6 @@
   </si>
   <si>
     <t>Fleet_3_Index</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
   </si>
 </sst>
 </file>
@@ -338,21 +311,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -360,71 +327,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -729,422 +640,364 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="17.15625" customWidth="1"/>
-    <col min="2" max="2" width="16.20703125" customWidth="1"/>
-    <col min="3" max="3" width="61.83984375" customWidth="1"/>
-    <col min="4" max="5" width="18.3125" customWidth="1"/>
-    <col min="6" max="16384" width="8.83984375" style="10"/>
-  </cols>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="7" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7" t="s">
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7" t="s">
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="12" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="12" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1155,2853 +1008,2260 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="10.9453125" style="1" customWidth="1"/>
-    <col min="2" max="6" width="14.3671875" customWidth="1"/>
-    <col min="7" max="7" width="14.3671875" style="1" customWidth="1"/>
-    <col min="8" max="12" width="14.3671875" customWidth="1"/>
-    <col min="13" max="13" width="14.3671875" style="1" customWidth="1"/>
-    <col min="14" max="18" width="14.3671875" customWidth="1"/>
-    <col min="19" max="19" width="14.3671875" style="1" customWidth="1"/>
-    <col min="20" max="26" width="14.3671875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="T1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="V1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="W1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="X1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="T1" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1971</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2">
         <v>16080.86</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="13">
+      <c r="G2">
         <v>2.343</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2">
         <v>14085.2</v>
       </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="11">
+      <c r="N2">
         <v>1257.8699999999999</v>
       </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="11">
+      <c r="T2">
         <v>737.79</v>
       </c>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1">
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>1972</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3">
         <v>15968.11</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="13">
+      <c r="G3">
         <v>1.488</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3">
         <v>13361</v>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="11">
+      <c r="N3">
         <v>1674.82</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="11">
+      <c r="T3">
         <v>932.29</v>
       </c>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1">
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>1973</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4">
         <v>17508.810000000001</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="13">
+      <c r="G4">
         <v>1.488</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4">
         <v>15954.1</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="11">
+      <c r="N4">
         <v>653.64</v>
       </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="11">
+      <c r="T4">
         <v>901.07</v>
       </c>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>1974</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5">
         <v>16205.45</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="13">
+      <c r="G5">
         <v>1.4930000000000001</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5">
         <v>12041.5</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="11">
+      <c r="N5">
         <v>3421.98</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="11">
+      <c r="T5">
         <v>741.97</v>
       </c>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="11"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1">
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>1975</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6">
         <v>20651.45</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="13">
+      <c r="G6">
         <v>1.496</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6">
         <v>15596.1</v>
       </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="11">
+      <c r="N6">
         <v>4380.45</v>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="11">
+      <c r="T6">
         <v>674.9</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1">
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>1976</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7">
         <v>13662.85</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="13">
+      <c r="G7">
         <v>1.4990000000000001</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7">
         <v>11721</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="11">
+      <c r="N7">
         <v>1130.01</v>
       </c>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="11">
+      <c r="T7">
         <v>811.84</v>
       </c>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="11"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1">
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>1977</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8">
         <v>17895.96</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="13">
+      <c r="G8">
         <v>1.4990000000000001</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8">
         <v>13773.1</v>
       </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="11">
+      <c r="N8">
         <v>3295.02</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="11">
+      <c r="T8">
         <v>827.84</v>
       </c>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="11"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1">
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>1978</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9">
         <v>20891</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="13">
+      <c r="G9">
         <v>1.492</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9">
         <v>15030.1</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="11">
+      <c r="N9">
         <v>3368.29</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="11">
+      <c r="T9">
         <v>2492.61</v>
       </c>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="11"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1">
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>1979</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10">
         <v>14636.6</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="13">
+      <c r="G10">
         <v>1.5109999999999999</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10">
         <v>10747.1</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="11">
+      <c r="N10">
         <v>924</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="11">
+      <c r="T10">
         <v>2965.5</v>
       </c>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1">
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>1980</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11">
         <v>22781.96</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="13">
+      <c r="G11">
         <v>1.5269999999999999</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11">
         <v>15858.4</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="11">
+      <c r="N11">
         <v>4902.49</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="11">
+      <c r="T11">
         <v>2021.07</v>
       </c>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="11"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1">
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>1981</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12">
         <v>24074.95</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="13">
+      <c r="G12">
         <v>1.538</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12">
         <v>16703.3</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="11">
+      <c r="N12">
         <v>6342.45</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="11">
+      <c r="T12">
         <v>1029.2</v>
       </c>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1">
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>1982</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13">
         <v>25741.59</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="13">
+      <c r="G13">
         <v>1.5629999999999999</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13">
         <v>18955.099999999999</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="11">
+      <c r="N13">
         <v>5331.14</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="11">
+      <c r="T13">
         <v>1455.35</v>
       </c>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="11"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1">
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>1983</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14">
         <v>35273.08</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="13">
+      <c r="G14">
         <v>1.5609999999999999</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14">
         <v>29552.3</v>
       </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="11">
+      <c r="N14">
         <v>3460.67</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="11">
+      <c r="T14">
         <v>2260.11</v>
       </c>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1">
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>1984</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15">
         <v>30212.67</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="13">
+      <c r="G15">
         <v>1.548</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15">
         <v>26285</v>
       </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="11">
+      <c r="N15">
         <v>2455.0100000000002</v>
       </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="11">
+      <c r="T15">
         <v>1472.66</v>
       </c>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1">
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>1985</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16">
         <v>36307.839999999997</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="13">
+      <c r="G16">
         <v>1.5289999999999999</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16">
         <v>30930.1</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="11">
+      <c r="N16">
         <v>3650.34</v>
       </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="11">
+      <c r="T16">
         <v>1727.4</v>
       </c>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1">
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>1986</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17">
         <v>47885.36</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="13">
+      <c r="G17">
         <v>1.4930000000000001</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17">
         <v>40424.300000000003</v>
       </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="11">
+      <c r="N17">
         <v>2928.4</v>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="11">
+      <c r="T17">
         <v>4532.66</v>
       </c>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="1">
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>1987</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18">
         <v>55483.14</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="13">
+      <c r="G18">
         <v>1.464</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18">
         <v>46343.1</v>
       </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="11">
+      <c r="N18">
         <v>2975.08</v>
       </c>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="11">
+      <c r="T18">
         <v>6164.96</v>
       </c>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="1">
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>1988</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19">
         <v>46984.9</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="13">
+      <c r="G19">
         <v>1.4179999999999999</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19">
         <v>39958.1</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="11">
+      <c r="N19">
         <v>2388.19</v>
       </c>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="11">
+      <c r="T19">
         <v>4638.6099999999997</v>
       </c>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="1">
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>1989</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20">
         <v>31439.73</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="13">
+      <c r="G20">
         <v>1.3420000000000001</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20">
         <v>23708.5</v>
       </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="11">
+      <c r="N20">
         <v>4532.7</v>
       </c>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="11">
+      <c r="T20">
         <v>3198.53</v>
       </c>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="1">
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>1990</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21">
         <v>31685.66</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="13">
+      <c r="G21">
         <v>1.2410000000000001</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21">
         <v>23875</v>
       </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="11">
+      <c r="N21">
         <v>3599.22</v>
       </c>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="11">
+      <c r="T21">
         <v>4211.4399999999996</v>
       </c>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="1">
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>1991</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22">
         <v>37640.879999999997</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="13">
+      <c r="G22">
         <v>1.1519999999999999</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22">
         <v>27080</v>
       </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="11">
+      <c r="N22">
         <v>3579.6</v>
       </c>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="11">
+      <c r="T22">
         <v>6981.28</v>
       </c>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1">
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>1992</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23">
         <v>36529.01</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="13">
+      <c r="G23">
         <v>1.0920000000000001</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23">
         <v>26434.799999999999</v>
       </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="11">
+      <c r="N23">
         <v>4509.07</v>
       </c>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="11">
+      <c r="T23">
         <v>5585.14</v>
       </c>
-      <c r="U23" s="11"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="11">
+      <c r="Y23">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="1">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>1993</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24">
         <v>43587.03</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24">
         <v>123.053</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11">
+      <c r="E24">
         <v>0.24</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24">
         <v>1.036</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24">
         <v>26605.4</v>
       </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="11">
+      <c r="N24">
         <v>5942.43</v>
       </c>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="11">
+      <c r="T24">
         <v>11039.2</v>
       </c>
-      <c r="U24" s="11">
+      <c r="U24">
         <v>123.053</v>
       </c>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11">
+      <c r="W24">
         <v>0.24</v>
       </c>
-      <c r="X24" s="11">
+      <c r="X24">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="Y24" s="11">
+      <c r="Y24">
         <v>0.115</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>1994</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25">
         <v>37242.050000000003</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25">
         <v>120.754</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11">
+      <c r="E25">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25">
         <v>0.02</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25">
         <v>0.97</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25">
         <v>25086.2</v>
       </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="11">
+      <c r="N25">
         <v>2526.12</v>
       </c>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="13">
+      <c r="S25">
         <v>1.03</v>
       </c>
-      <c r="T25" s="11">
+      <c r="T25">
         <v>9629.73</v>
       </c>
-      <c r="U25" s="11">
+      <c r="U25">
         <v>120.754</v>
       </c>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11">
+      <c r="W25">
         <v>0.28999999999999998</v>
       </c>
-      <c r="X25" s="11">
+      <c r="X25">
         <v>0.02</v>
       </c>
-      <c r="Y25" s="11">
+      <c r="Y25">
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="1">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>1995</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26">
         <v>40525.19</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26">
         <v>133.143</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11">
+      <c r="E26">
         <v>0.28699999999999998</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26">
         <v>0.91600000000000004</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26">
         <v>28919.7</v>
       </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="11">
+      <c r="N26">
         <v>2813.01</v>
       </c>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="13">
+      <c r="S26">
         <v>1.17</v>
       </c>
-      <c r="T26" s="11">
+      <c r="T26">
         <v>8792.48</v>
       </c>
-      <c r="U26" s="11">
+      <c r="U26">
         <v>133.143</v>
       </c>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11">
+      <c r="W26">
         <v>0.28699999999999998</v>
       </c>
-      <c r="X26" s="11">
+      <c r="X26">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="Y26" s="11">
+      <c r="Y26">
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="1">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>1996</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27">
         <v>35865.919999999998</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="13">
+      <c r="G27">
         <v>0.84799999999999998</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27">
         <v>22971.8</v>
       </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="11">
+      <c r="N27">
         <v>4179.26</v>
       </c>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
-      <c r="S27" s="13">
+      <c r="S27">
         <v>1.01</v>
       </c>
-      <c r="T27" s="11">
+      <c r="T27">
         <v>8714.86</v>
       </c>
-      <c r="U27" s="11"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="11">
+      <c r="Y27">
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="1">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>1997</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28">
         <v>34284.99</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28">
         <v>153.69300000000001</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11">
+      <c r="E28">
         <v>0.28499999999999998</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28">
         <v>0.224</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28">
         <v>0.79500000000000004</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28">
         <v>24497.4</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28">
         <v>135.768</v>
       </c>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11">
+      <c r="K28">
         <v>0.309</v>
       </c>
-      <c r="L28" s="11">
+      <c r="L28">
         <v>0.11799999999999999</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28">
         <v>0.74299999999999999</v>
       </c>
-      <c r="N28" s="11">
+      <c r="N28">
         <v>4191.43</v>
       </c>
-      <c r="O28" s="11">
+      <c r="O28">
         <v>178.42699999999999</v>
       </c>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11">
+      <c r="Q28">
         <v>0.20200000000000001</v>
       </c>
-      <c r="R28" s="11">
+      <c r="R28">
         <v>0.35199999999999998</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28">
         <v>1.06</v>
       </c>
-      <c r="T28" s="11">
+      <c r="T28">
         <v>5596.16</v>
       </c>
-      <c r="U28" s="11">
+      <c r="U28">
         <v>150.28899999999999</v>
       </c>
-      <c r="V28" s="11"/>
-      <c r="W28" s="11">
+      <c r="W28">
         <v>0.315</v>
       </c>
-      <c r="X28" s="11">
+      <c r="X28">
         <v>0.21299999999999999</v>
       </c>
-      <c r="Y28" s="11">
+      <c r="Y28">
         <v>0.66300000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="1">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>1998</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29">
         <v>30604.34</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29">
         <v>178.17500000000001</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11">
+      <c r="E29">
         <v>0.223</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29">
         <v>0.38500000000000001</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29">
         <v>0.72499999999999998</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29">
         <v>22504.3</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29">
         <v>148.95400000000001</v>
       </c>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11">
+      <c r="K29">
         <v>0.29199999999999998</v>
       </c>
-      <c r="L29" s="11">
+      <c r="L29">
         <v>0.189</v>
       </c>
-      <c r="M29" s="13">
+      <c r="M29">
         <v>0.71899999999999997</v>
       </c>
-      <c r="N29" s="11">
+      <c r="N29">
         <v>3460.87</v>
       </c>
-      <c r="O29" s="11">
+      <c r="O29">
         <v>182.91900000000001</v>
       </c>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11">
+      <c r="Q29">
         <v>0.18</v>
       </c>
-      <c r="R29" s="11">
+      <c r="R29">
         <v>0.35399999999999998</v>
       </c>
-      <c r="S29" s="13">
+      <c r="S29">
         <v>0.93</v>
       </c>
-      <c r="T29" s="11">
+      <c r="T29">
         <v>4639.17</v>
       </c>
-      <c r="U29" s="11">
+      <c r="U29">
         <v>202.65299999999999</v>
       </c>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11">
+      <c r="W29">
         <v>0.19700000000000001</v>
       </c>
-      <c r="X29" s="11">
+      <c r="X29">
         <v>0.61199999999999999</v>
       </c>
-      <c r="Y29" s="11">
+      <c r="Y29">
         <v>0.68400000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="1">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>1999</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30">
         <v>29885.53</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30">
         <v>171.351</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11">
+      <c r="E30">
         <v>0.187</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30">
         <v>0.36</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30">
         <v>0.65400000000000003</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30">
         <v>21811.3</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30">
         <v>142.91</v>
       </c>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11">
+      <c r="K30">
         <v>0.26800000000000002</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30">
         <v>0.126</v>
       </c>
-      <c r="M30" s="13">
+      <c r="M30">
         <v>0.84499999999999997</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30">
         <v>3149.59</v>
       </c>
-      <c r="O30" s="11">
+      <c r="O30">
         <v>199.792</v>
       </c>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11">
+      <c r="Q30">
         <v>0.107</v>
       </c>
-      <c r="R30" s="11">
+      <c r="R30">
         <v>0.59399999999999997</v>
       </c>
-      <c r="S30" s="13">
+      <c r="S30">
         <v>0.64</v>
       </c>
-      <c r="T30" s="11">
+      <c r="T30">
         <v>4924.6400000000003</v>
       </c>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11">
+      <c r="Y30">
         <v>0.56799999999999995</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="1">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>2000</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31">
         <v>31866.959999999999</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31">
         <v>158.434</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11">
+      <c r="E31">
         <v>0.27700000000000002</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31">
         <v>0.24199999999999999</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31">
         <v>0.61199999999999999</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31">
         <v>24111.9</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31">
         <v>138.334</v>
       </c>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11">
+      <c r="K31">
         <v>0.29899999999999999</v>
       </c>
-      <c r="L31" s="11">
+      <c r="L31">
         <v>0.106</v>
       </c>
-      <c r="M31" s="13">
+      <c r="M31">
         <v>1.139</v>
       </c>
-      <c r="N31" s="11">
+      <c r="N31">
         <v>2838.4</v>
       </c>
-      <c r="O31" s="11">
+      <c r="O31">
         <v>178.53399999999999</v>
       </c>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11">
+      <c r="Q31">
         <v>0.255</v>
       </c>
-      <c r="R31" s="11">
+      <c r="R31">
         <v>0.379</v>
       </c>
-      <c r="S31" s="13">
+      <c r="S31">
         <v>0.71</v>
       </c>
-      <c r="T31" s="11">
+      <c r="T31">
         <v>4916.66</v>
       </c>
-      <c r="U31" s="11"/>
-      <c r="V31" s="11"/>
-      <c r="W31" s="11"/>
-      <c r="X31" s="11"/>
-      <c r="Y31" s="11">
+      <c r="Y31">
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="1">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A32">
         <v>2001</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32">
         <v>25045.040000000001</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32">
         <v>147.62200000000001</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11">
+      <c r="E32">
         <v>0.25800000000000001</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32">
         <v>0.11899999999999999</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32">
         <v>0.58899999999999997</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32">
         <v>17361.7</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32">
         <v>136.54599999999999</v>
       </c>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11">
+      <c r="K32">
         <v>0.31</v>
       </c>
-      <c r="L32" s="11">
+      <c r="L32">
         <v>0.111</v>
       </c>
-      <c r="M32" s="13">
+      <c r="M32">
         <v>1.0329999999999999</v>
       </c>
-      <c r="N32" s="11">
+      <c r="N32">
         <v>2723.72</v>
       </c>
-      <c r="O32" s="11">
+      <c r="O32">
         <v>158.697</v>
       </c>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11">
+      <c r="Q32">
         <v>0.20599999999999999</v>
       </c>
-      <c r="R32" s="11">
+      <c r="R32">
         <v>0.127</v>
       </c>
-      <c r="S32" s="13">
+      <c r="S32">
         <v>0.74</v>
       </c>
-      <c r="T32" s="11">
+      <c r="T32">
         <v>4959.62</v>
       </c>
-      <c r="U32" s="11"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="11">
+      <c r="Y32">
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="1">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>2002</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33">
         <v>22742.16</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33">
         <v>145.655</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11">
+      <c r="E33">
         <v>0.22800000000000001</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33">
         <v>0.56200000000000006</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33">
         <v>15665.9</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33">
         <v>139.012</v>
       </c>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11">
+      <c r="K33">
         <v>0.25600000000000001</v>
       </c>
-      <c r="L33" s="11">
+      <c r="L33">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="M33" s="13">
+      <c r="M33">
         <v>0.88800000000000001</v>
       </c>
-      <c r="N33" s="11">
+      <c r="N33">
         <v>1890.03</v>
       </c>
-      <c r="O33" s="11">
+      <c r="O33">
         <v>152.298</v>
       </c>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11">
+      <c r="Q33">
         <v>0.2</v>
       </c>
-      <c r="R33" s="11">
+      <c r="R33">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="S33" s="13">
+      <c r="S33">
         <v>0.53</v>
       </c>
-      <c r="T33" s="11">
+      <c r="T33">
         <v>5186.2299999999996</v>
       </c>
-      <c r="U33" s="11"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="11">
+      <c r="Y33">
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="1">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>2003</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34">
         <v>26860.53</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34">
         <v>156.98500000000001</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11">
+      <c r="E34">
         <v>0.22700000000000001</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34">
         <v>0.13100000000000001</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34">
         <v>0.52900000000000003</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34">
         <v>15974.5</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34">
         <v>146.36199999999999</v>
       </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11">
+      <c r="K34">
         <v>0.27200000000000002</v>
       </c>
-      <c r="L34" s="11">
+      <c r="L34">
         <v>0.11600000000000001</v>
       </c>
-      <c r="M34" s="13">
+      <c r="M34">
         <v>1.0309999999999999</v>
       </c>
-      <c r="N34" s="11">
+      <c r="N34">
         <v>3097.72</v>
       </c>
-      <c r="O34" s="11">
+      <c r="O34">
         <v>153.09800000000001</v>
       </c>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11">
+      <c r="Q34">
         <v>0.16900000000000001</v>
       </c>
-      <c r="R34" s="11">
+      <c r="R34">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="S34" s="13">
+      <c r="S34">
         <v>0.77</v>
       </c>
-      <c r="T34" s="11">
+      <c r="T34">
         <v>7788.31</v>
       </c>
-      <c r="U34" s="11">
+      <c r="U34">
         <v>171.49600000000001</v>
       </c>
-      <c r="V34" s="11"/>
-      <c r="W34" s="11">
+      <c r="W34">
         <v>0.23799999999999999</v>
       </c>
-      <c r="X34" s="11">
+      <c r="X34">
         <v>0.23899999999999999</v>
       </c>
-      <c r="Y34" s="11">
+      <c r="Y34">
         <v>0.89300000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="1">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>2004</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35">
         <v>25265.55</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35">
         <v>150.958</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11">
+      <c r="E35">
         <v>0.251</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35">
         <v>0.108</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35">
         <v>0.503</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35">
         <v>17313.900000000001</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35">
         <v>147.11099999999999</v>
       </c>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11">
+      <c r="K35">
         <v>0.28499999999999998</v>
       </c>
-      <c r="L35" s="11">
+      <c r="L35">
         <v>0.14299999999999999</v>
       </c>
-      <c r="M35" s="13">
+      <c r="M35">
         <v>0.93</v>
       </c>
-      <c r="N35" s="11">
+      <c r="N35">
         <v>3194.83</v>
       </c>
-      <c r="O35" s="11">
+      <c r="O35">
         <v>148.96199999999999</v>
       </c>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11">
+      <c r="Q35">
         <v>0.19800000000000001</v>
       </c>
-      <c r="R35" s="11">
+      <c r="R35">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="S35" s="13">
+      <c r="S35">
         <v>0.53</v>
       </c>
-      <c r="T35" s="11">
+      <c r="T35">
         <v>4756.82</v>
       </c>
-      <c r="U35" s="11">
+      <c r="U35">
         <v>156.80000000000001</v>
       </c>
-      <c r="V35" s="11"/>
-      <c r="W35" s="11">
+      <c r="W35">
         <v>0.26900000000000002</v>
       </c>
-      <c r="X35" s="11">
+      <c r="X35">
         <v>0.14899999999999999</v>
       </c>
-      <c r="Y35" s="11">
+      <c r="Y35">
         <v>1.036</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="1">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>2005</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36">
         <v>25009.45</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36">
         <v>150.547</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11">
+      <c r="E36">
         <v>0.22900000000000001</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36">
         <v>0.112</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36">
         <v>0.49</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36">
         <v>15006.1</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36">
         <v>136.94499999999999</v>
       </c>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11">
+      <c r="K36">
         <v>0.27500000000000002</v>
       </c>
-      <c r="L36" s="11">
+      <c r="L36">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="M36" s="13">
+      <c r="M36">
         <v>0.89100000000000001</v>
       </c>
-      <c r="N36" s="11">
+      <c r="N36">
         <v>3530.98</v>
       </c>
-      <c r="O36" s="11">
+      <c r="O36">
         <v>143.38399999999999</v>
       </c>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11">
+      <c r="Q36">
         <v>0.20599999999999999</v>
       </c>
-      <c r="R36" s="11">
+      <c r="R36">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="S36" s="13">
+      <c r="S36">
         <v>0.69</v>
       </c>
-      <c r="T36" s="11">
+      <c r="T36">
         <v>6472.37</v>
       </c>
-      <c r="U36" s="11">
+      <c r="U36">
         <v>171.31100000000001</v>
       </c>
-      <c r="V36" s="11"/>
-      <c r="W36" s="11">
+      <c r="W36">
         <v>0.20599999999999999</v>
       </c>
-      <c r="X36" s="11">
+      <c r="X36">
         <v>0.22600000000000001</v>
       </c>
-      <c r="Y36" s="11">
+      <c r="Y36">
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="1">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>2006</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37">
         <v>24639.3</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37">
         <v>160.55799999999999</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11">
+      <c r="E37">
         <v>0.223</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37">
         <v>0.26</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37">
         <v>0.47399999999999998</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37">
         <v>15463.6</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37">
         <v>145.04599999999999</v>
       </c>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11">
+      <c r="K37">
         <v>0.31</v>
       </c>
-      <c r="L37" s="11">
+      <c r="L37">
         <v>0.17699999999999999</v>
       </c>
-      <c r="M37" s="13">
+      <c r="M37">
         <v>0.88400000000000001</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37">
         <v>2824.18</v>
       </c>
-      <c r="O37" s="11">
+      <c r="O37">
         <v>139.65100000000001</v>
       </c>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11">
+      <c r="Q37">
         <v>0.23899999999999999</v>
       </c>
-      <c r="R37" s="11">
+      <c r="R37">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="S37" s="13">
+      <c r="S37">
         <v>0.87</v>
       </c>
-      <c r="T37" s="11">
+      <c r="T37">
         <v>6351.52</v>
       </c>
-      <c r="U37" s="11">
+      <c r="U37">
         <v>196.977</v>
       </c>
-      <c r="V37" s="11"/>
-      <c r="W37" s="11">
+      <c r="W37">
         <v>0.121</v>
       </c>
-      <c r="X37" s="11">
+      <c r="X37">
         <v>0.55800000000000005</v>
       </c>
-      <c r="Y37" s="11">
+      <c r="Y37">
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="1">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>2007</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38">
         <v>27276.78</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38">
         <v>136.46299999999999</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11">
+      <c r="E38">
         <v>0.24</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38">
         <v>0.47499999999999998</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38">
         <v>17038.5</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38">
         <v>130.17699999999999</v>
       </c>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11">
+      <c r="K38">
         <v>0.28799999999999998</v>
       </c>
-      <c r="L38" s="11">
+      <c r="L38">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="M38" s="13">
+      <c r="M38">
         <v>0.998</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38">
         <v>2270.9899999999998</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38">
         <v>150.65899999999999</v>
       </c>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11">
+      <c r="Q38">
         <v>0.223</v>
       </c>
-      <c r="R38" s="11">
+      <c r="R38">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S38" s="13">
+      <c r="S38">
         <v>1.02</v>
       </c>
-      <c r="T38" s="11">
+      <c r="T38">
         <v>7967.29</v>
       </c>
-      <c r="U38" s="11">
+      <c r="U38">
         <v>128.554</v>
       </c>
-      <c r="V38" s="11"/>
-      <c r="W38" s="11">
+      <c r="W38">
         <v>0.21099999999999999</v>
       </c>
-      <c r="X38" s="11">
+      <c r="X38">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="Y38" s="11">
+      <c r="Y38">
         <v>0.69399999999999995</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="1">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>2008</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39">
         <v>31378.959999999999</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39">
         <v>158.57599999999999</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11">
+      <c r="E39">
         <v>0.23200000000000001</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39">
         <v>0.26100000000000001</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39">
         <v>0.48099999999999998</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39">
         <v>20787.8</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39">
         <v>145.666</v>
       </c>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11">
+      <c r="K39">
         <v>0.30299999999999999</v>
       </c>
-      <c r="L39" s="11">
+      <c r="L39">
         <v>0.14199999999999999</v>
       </c>
-      <c r="M39" s="13">
+      <c r="M39">
         <v>1.1539999999999999</v>
       </c>
-      <c r="N39" s="11">
+      <c r="N39">
         <v>3186.59</v>
       </c>
-      <c r="O39" s="11">
+      <c r="O39">
         <v>154.95599999999999</v>
       </c>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11">
+      <c r="Q39">
         <v>0.23300000000000001</v>
       </c>
-      <c r="R39" s="11">
+      <c r="R39">
         <v>0.122</v>
       </c>
-      <c r="S39" s="13">
+      <c r="S39">
         <v>1.49</v>
       </c>
-      <c r="T39" s="11">
+      <c r="T39">
         <v>7404.57</v>
       </c>
-      <c r="U39" s="11">
+      <c r="U39">
         <v>166.84</v>
       </c>
-      <c r="V39" s="11"/>
-      <c r="W39" s="11">
+      <c r="W39">
         <v>0.19600000000000001</v>
       </c>
-      <c r="X39" s="11">
+      <c r="X39">
         <v>0.39</v>
       </c>
-      <c r="Y39" s="11">
+      <c r="Y39">
         <v>0.66</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="1">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A40">
         <v>2009</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40">
         <v>36134.83</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40">
         <v>188.149</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11">
+      <c r="E40">
         <v>0.193</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40">
         <v>0.505</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40">
         <v>0.49</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40">
         <v>24465.5</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40">
         <v>154.66399999999999</v>
       </c>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11">
+      <c r="K40">
         <v>0.30499999999999999</v>
       </c>
-      <c r="L40" s="11">
+      <c r="L40">
         <v>0.22500000000000001</v>
       </c>
-      <c r="M40" s="13">
+      <c r="M40">
         <v>1.095</v>
       </c>
-      <c r="N40" s="11">
+      <c r="N40">
         <v>2942.14</v>
       </c>
-      <c r="O40" s="11">
+      <c r="O40">
         <v>169.874</v>
       </c>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11">
+      <c r="Q40">
         <v>0.20899999999999999</v>
       </c>
-      <c r="R40" s="11">
+      <c r="R40">
         <v>0.24</v>
       </c>
-      <c r="S40" s="13">
+      <c r="S40">
         <v>1.24</v>
       </c>
-      <c r="T40" s="11">
+      <c r="T40">
         <v>8727.19</v>
       </c>
-      <c r="U40" s="11">
+      <c r="U40">
         <v>214.03</v>
       </c>
-      <c r="V40" s="11"/>
-      <c r="W40" s="11">
+      <c r="W40">
         <v>0.129</v>
       </c>
-      <c r="X40" s="11">
+      <c r="X40">
         <v>0.77700000000000002</v>
       </c>
-      <c r="Y40" s="11">
+      <c r="Y40">
         <v>0.68700000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="1">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A41">
         <v>2010</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41">
         <v>38171.74</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41">
         <v>160.71700000000001</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11">
+      <c r="E41">
         <v>0.215</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41">
         <v>0.29699999999999999</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41">
         <v>0.49199999999999999</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41">
         <v>26094.3</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41">
         <v>146.851</v>
       </c>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11">
+      <c r="K41">
         <v>0.315</v>
       </c>
-      <c r="L41" s="11">
+      <c r="L41">
         <v>0.188</v>
       </c>
-      <c r="M41" s="13">
+      <c r="M41">
         <v>1.073</v>
       </c>
-      <c r="N41" s="11">
+      <c r="N41">
         <v>2755.04</v>
       </c>
-      <c r="O41" s="11">
+      <c r="O41">
         <v>164.167</v>
       </c>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11">
+      <c r="Q41">
         <v>0.185</v>
       </c>
-      <c r="R41" s="11">
+      <c r="R41">
         <v>0.10299999999999999</v>
       </c>
-      <c r="S41" s="13">
+      <c r="S41">
         <v>1.44</v>
       </c>
-      <c r="T41" s="11">
+      <c r="T41">
         <v>9322.4</v>
       </c>
-      <c r="U41" s="11">
+      <c r="U41">
         <v>164.18899999999999</v>
       </c>
-      <c r="V41" s="11"/>
-      <c r="W41" s="11">
+      <c r="W41">
         <v>0.192</v>
       </c>
-      <c r="X41" s="11">
+      <c r="X41">
         <v>0.39800000000000002</v>
       </c>
-      <c r="Y41" s="11">
+      <c r="Y41">
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="1">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A42">
         <v>2011</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42">
         <v>39006.980000000003</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42">
         <v>171.11</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11">
+      <c r="E42">
         <v>0.184</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42">
         <v>0.36199999999999999</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42">
         <v>0.499</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42">
         <v>27988.2</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42">
         <v>134.45500000000001</v>
       </c>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11">
+      <c r="K42">
         <v>0.309</v>
       </c>
-      <c r="L42" s="11">
+      <c r="L42">
         <v>0.10299999999999999</v>
       </c>
-      <c r="M42" s="13">
+      <c r="M42">
         <v>1.1140000000000001</v>
       </c>
-      <c r="N42" s="11">
+      <c r="N42">
         <v>2147.89</v>
       </c>
-      <c r="O42" s="11">
+      <c r="O42">
         <v>188.97900000000001</v>
       </c>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11">
+      <c r="Q42">
         <v>0.16200000000000001</v>
       </c>
-      <c r="R42" s="11">
+      <c r="R42">
         <v>0.44700000000000001</v>
       </c>
-      <c r="S42" s="13">
+      <c r="S42">
         <v>1.1499999999999999</v>
       </c>
-      <c r="T42" s="11">
+      <c r="T42">
         <v>8870.89</v>
       </c>
-      <c r="U42" s="11">
+      <c r="U42">
         <v>175.80600000000001</v>
       </c>
-      <c r="V42" s="11"/>
-      <c r="W42" s="11">
+      <c r="W42">
         <v>0.158</v>
       </c>
-      <c r="X42" s="11">
+      <c r="X42">
         <v>0.40500000000000003</v>
       </c>
-      <c r="Y42" s="11">
+      <c r="Y42">
         <v>1.129</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="1">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>2012</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43">
         <v>36604.81</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43">
         <v>170.041</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11">
+      <c r="E43">
         <v>0.22</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43">
         <v>0.34100000000000003</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43">
         <v>0.51500000000000001</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43">
         <v>28665.8</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43">
         <v>136.083</v>
       </c>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11">
+      <c r="K43">
         <v>0.27800000000000002</v>
       </c>
-      <c r="L43" s="11">
+      <c r="L43">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="M43" s="13">
+      <c r="M43">
         <v>1.0960000000000001</v>
       </c>
-      <c r="N43" s="11">
+      <c r="N43">
         <v>2256.35</v>
       </c>
-      <c r="O43" s="11">
+      <c r="O43">
         <v>163.05699999999999</v>
       </c>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11">
+      <c r="Q43">
         <v>0.25600000000000001</v>
       </c>
-      <c r="R43" s="11">
+      <c r="R43">
         <v>0.251</v>
       </c>
-      <c r="S43" s="13">
+      <c r="S43">
         <v>1.63</v>
       </c>
-      <c r="T43" s="11">
+      <c r="T43">
         <v>5682.66</v>
       </c>
-      <c r="U43" s="11">
+      <c r="U43">
         <v>183.68799999999999</v>
       </c>
-      <c r="V43" s="11"/>
-      <c r="W43" s="11">
+      <c r="W43">
         <v>0.189</v>
       </c>
-      <c r="X43" s="11">
+      <c r="X43">
         <v>0.45400000000000001</v>
       </c>
-      <c r="Y43" s="11">
+      <c r="Y43">
         <v>1.298</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="1">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A44">
         <v>2013</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44">
         <v>36747.89</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44">
         <v>166.714</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11">
+      <c r="E44">
         <v>0.21299999999999999</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44">
         <v>0.27800000000000002</v>
       </c>
-      <c r="G44" s="13">
+      <c r="G44">
         <v>0.54200000000000004</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44">
         <v>28562</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44">
         <v>132.26499999999999</v>
       </c>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11">
+      <c r="K44">
         <v>0.29099999999999998</v>
       </c>
-      <c r="L44" s="11">
+      <c r="L44">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="M44" s="13">
+      <c r="M44">
         <v>1.149</v>
       </c>
-      <c r="N44" s="11">
+      <c r="N44">
         <v>1353.72</v>
       </c>
-      <c r="O44" s="11">
+      <c r="O44">
         <v>186.846</v>
       </c>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="11">
+      <c r="Q44">
         <v>0.16900000000000001</v>
       </c>
-      <c r="R44" s="11">
+      <c r="R44">
         <v>0.433</v>
       </c>
-      <c r="S44" s="13">
+      <c r="S44">
         <v>1.26</v>
       </c>
-      <c r="T44" s="11">
+      <c r="T44">
         <v>6832.17</v>
       </c>
-      <c r="U44" s="11">
+      <c r="U44">
         <v>173.87200000000001</v>
       </c>
-      <c r="V44" s="11"/>
-      <c r="W44" s="11">
+      <c r="W44">
         <v>0.19600000000000001</v>
       </c>
-      <c r="X44" s="11">
+      <c r="X44">
         <v>0.29899999999999999</v>
       </c>
-      <c r="Y44" s="11">
+      <c r="Y44">
         <v>1.1060000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="1">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A45">
         <v>2014</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45">
         <v>38133.19</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45">
         <v>174.81100000000001</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11">
+      <c r="E45">
         <v>0.20200000000000001</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45">
         <v>0.38600000000000001</v>
       </c>
-      <c r="G45" s="13">
+      <c r="G45">
         <v>0.57299999999999995</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45">
         <v>29041.1</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45">
         <v>128.87700000000001</v>
       </c>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11">
+      <c r="K45">
         <v>0.30199999999999999</v>
       </c>
-      <c r="L45" s="11">
+      <c r="L45">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="M45" s="13">
+      <c r="M45">
         <v>1.085</v>
       </c>
-      <c r="N45" s="11">
+      <c r="N45">
         <v>3286.88</v>
       </c>
-      <c r="O45" s="11">
+      <c r="O45">
         <v>185.571</v>
       </c>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11">
+      <c r="Q45">
         <v>0.16800000000000001</v>
       </c>
-      <c r="R45" s="11">
+      <c r="R45">
         <v>0.441</v>
       </c>
-      <c r="S45" s="13">
+      <c r="S45">
         <v>1.36</v>
       </c>
-      <c r="T45" s="11">
+      <c r="T45">
         <v>5805.21</v>
       </c>
-      <c r="U45" s="11">
+      <c r="U45">
         <v>192.398</v>
       </c>
-      <c r="V45" s="11"/>
-      <c r="W45" s="11">
+      <c r="W45">
         <v>0.16800000000000001</v>
       </c>
-      <c r="X45" s="11">
+      <c r="X45">
         <v>0.50900000000000001</v>
       </c>
-      <c r="Y45" s="11">
+      <c r="Y45">
         <v>1.597</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="1">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A46">
         <v>2015</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46">
         <v>40190.769999999997</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46">
         <v>156.99299999999999</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11">
+      <c r="E46">
         <v>0.221</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46">
         <v>0.19400000000000001</v>
       </c>
-      <c r="G46" s="13">
+      <c r="G46">
         <v>0.58799999999999997</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46">
         <v>30078.3</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46">
         <v>134.78899999999999</v>
       </c>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11">
+      <c r="K46">
         <v>0.254</v>
       </c>
-      <c r="L46" s="11">
+      <c r="L46">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="M46" s="13">
+      <c r="M46">
         <v>1.1240000000000001</v>
       </c>
-      <c r="N46" s="11">
+      <c r="N46">
         <v>4011.13</v>
       </c>
-      <c r="O46" s="11">
+      <c r="O46">
         <v>175.64500000000001</v>
       </c>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11">
+      <c r="Q46">
         <v>0.18099999999999999</v>
       </c>
-      <c r="R46" s="11">
+      <c r="R46">
         <v>0.32100000000000001</v>
       </c>
-      <c r="S46" s="13">
+      <c r="S46">
         <v>1.37</v>
       </c>
-      <c r="T46" s="11">
+      <c r="T46">
         <v>6101.34</v>
       </c>
-      <c r="U46" s="11">
+      <c r="U46">
         <v>160.54400000000001</v>
       </c>
-      <c r="V46" s="11"/>
-      <c r="W46" s="11">
+      <c r="W46">
         <v>0.22900000000000001</v>
       </c>
-      <c r="X46" s="11">
+      <c r="X46">
         <v>0.19700000000000001</v>
       </c>
-      <c r="Y46" s="11">
+      <c r="Y46">
         <v>1.984</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="1">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A47">
         <v>2016</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47">
         <v>44085.46</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47">
         <v>168.09</v>
       </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11">
+      <c r="E47">
         <v>0.20100000000000001</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47">
         <v>0.251</v>
       </c>
-      <c r="G47" s="13">
+      <c r="G47">
         <v>0.58699999999999997</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47">
         <v>29018.7</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47">
         <v>143</v>
       </c>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11">
+      <c r="K47">
         <v>0.26700000000000002</v>
       </c>
-      <c r="L47" s="11">
+      <c r="L47">
         <v>0.113</v>
       </c>
-      <c r="M47" s="13">
+      <c r="M47">
         <v>1.026</v>
       </c>
-      <c r="N47" s="11">
+      <c r="N47">
         <v>4217.09</v>
       </c>
-      <c r="O47" s="11">
+      <c r="O47">
         <v>187.56399999999999</v>
       </c>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="11">
+      <c r="Q47">
         <v>0.16400000000000001</v>
       </c>
-      <c r="R47" s="11">
+      <c r="R47">
         <v>0.44800000000000001</v>
       </c>
-      <c r="S47" s="13">
+      <c r="S47">
         <v>1.17</v>
       </c>
-      <c r="T47" s="11">
+      <c r="T47">
         <v>10849.67</v>
       </c>
-      <c r="U47" s="11">
+      <c r="U47">
         <v>170.89699999999999</v>
       </c>
-      <c r="V47" s="11"/>
-      <c r="W47" s="11">
+      <c r="W47">
         <v>0.186</v>
       </c>
-      <c r="X47" s="11">
+      <c r="X47">
         <v>0.221</v>
       </c>
-      <c r="Y47" s="11">
+      <c r="Y47">
         <v>2.2010000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="1">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A48">
         <v>2017</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48">
         <v>40004.480000000003</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48">
         <v>178.16900000000001</v>
       </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11">
+      <c r="E48">
         <v>0.17899999999999999</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48">
         <v>0.38400000000000001</v>
       </c>
-      <c r="G48" s="13">
+      <c r="G48">
         <v>0.60599999999999998</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48">
         <v>27316.5</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48">
         <v>146.54400000000001</v>
       </c>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11">
+      <c r="K48">
         <v>0.25700000000000001</v>
       </c>
-      <c r="L48" s="11">
+      <c r="L48">
         <v>0.125</v>
       </c>
-      <c r="M48" s="13">
+      <c r="M48">
         <v>0.97599999999999998</v>
       </c>
-      <c r="N48" s="11">
+      <c r="N48">
         <v>4443.8500000000004</v>
       </c>
-      <c r="O48" s="11">
+      <c r="O48">
         <v>189.34</v>
       </c>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="11">
+      <c r="Q48">
         <v>0.14699999999999999</v>
       </c>
-      <c r="R48" s="11">
+      <c r="R48">
         <v>0.45700000000000002</v>
       </c>
-      <c r="S48" s="13">
+      <c r="S48">
         <v>1.1299999999999999</v>
       </c>
-      <c r="T48" s="11">
+      <c r="T48">
         <v>8244.1299999999992</v>
       </c>
-      <c r="U48" s="11">
+      <c r="U48">
         <v>188.39599999999999</v>
       </c>
-      <c r="V48" s="11"/>
-      <c r="W48" s="11">
+      <c r="W48">
         <v>0.156</v>
       </c>
-      <c r="X48" s="11">
+      <c r="X48">
         <v>0.47799999999999998</v>
       </c>
-      <c r="Y48" s="11">
+      <c r="Y48">
         <v>1.964</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="1">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A49">
         <v>2018</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49">
         <v>33978.71</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49">
         <v>168.21700000000001</v>
       </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11">
+      <c r="E49">
         <v>0.216</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49">
         <v>0.309</v>
       </c>
-      <c r="G49" s="13">
+      <c r="G49">
         <v>0.64600000000000002</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49">
         <v>21684.7</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49">
         <v>134.738</v>
       </c>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11">
+      <c r="K49">
         <v>0.252</v>
       </c>
-      <c r="L49" s="11">
+      <c r="L49">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="M49" s="13">
+      <c r="M49">
         <v>0.96199999999999997</v>
       </c>
-      <c r="N49" s="11">
+      <c r="N49">
         <v>4111.12</v>
       </c>
-      <c r="O49" s="11">
+      <c r="O49">
         <v>179.28800000000001</v>
       </c>
-      <c r="P49" s="11"/>
-      <c r="Q49" s="11">
+      <c r="Q49">
         <v>0.189</v>
       </c>
-      <c r="R49" s="11">
+      <c r="R49">
         <v>0.38500000000000001</v>
       </c>
-      <c r="S49" s="13">
+      <c r="S49">
         <v>0.74</v>
       </c>
-      <c r="T49" s="11">
+      <c r="T49">
         <v>8182.89</v>
       </c>
-      <c r="U49" s="11">
+      <c r="U49">
         <v>175.68700000000001</v>
       </c>
-      <c r="V49" s="11"/>
-      <c r="W49" s="11">
+      <c r="W49">
         <v>0.21299999999999999</v>
       </c>
-      <c r="X49" s="11">
+      <c r="X49">
         <v>0.36199999999999999</v>
       </c>
-      <c r="Y49" s="11">
+      <c r="Y49">
         <v>1.7270000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="1">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A50">
         <v>2019</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50">
         <v>27212.29</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50">
         <v>168.405</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11">
+      <c r="E50">
         <v>0.22800000000000001</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50">
         <v>0.32800000000000001</v>
       </c>
-      <c r="G50" s="13">
+      <c r="G50">
         <v>0.66200000000000003</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50">
         <v>16314.2</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50">
         <v>134.149</v>
       </c>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11">
+      <c r="K50">
         <v>0.28699999999999998</v>
       </c>
-      <c r="L50" s="11">
+      <c r="L50">
         <v>0.09</v>
       </c>
-      <c r="M50" s="13">
+      <c r="M50">
         <v>0.95299999999999996</v>
       </c>
-      <c r="N50" s="11">
+      <c r="N50">
         <v>3855.22</v>
       </c>
-      <c r="O50" s="11">
+      <c r="O50">
         <v>183.38800000000001</v>
       </c>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11">
+      <c r="Q50">
         <v>0.19900000000000001</v>
       </c>
-      <c r="R50" s="11">
+      <c r="R50">
         <v>0.46</v>
       </c>
-      <c r="S50" s="13">
+      <c r="S50">
         <v>0.91</v>
       </c>
-      <c r="T50" s="11">
+      <c r="T50">
         <v>7042.87</v>
       </c>
-      <c r="U50" s="11">
+      <c r="U50">
         <v>178.042</v>
       </c>
-      <c r="V50" s="11"/>
-      <c r="W50" s="11">
+      <c r="W50">
         <v>0.21199999999999999</v>
       </c>
-      <c r="X50" s="11">
+      <c r="X50">
         <v>0.38100000000000001</v>
       </c>
-      <c r="Y50" s="11">
+      <c r="Y50">
         <v>2.0870000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="1">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A51">
         <v>2020</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51">
         <v>21147.41</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51">
         <v>167.97</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11">
+      <c r="E51">
         <v>0.17799999999999999</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51">
         <v>0.30499999999999999</v>
       </c>
-      <c r="G51" s="13">
+      <c r="G51">
         <v>0.67500000000000004</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51">
         <v>12324.9</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51">
         <v>157.12100000000001</v>
       </c>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11">
+      <c r="K51">
         <v>0.23300000000000001</v>
       </c>
-      <c r="L51" s="11">
+      <c r="L51">
         <v>0.183</v>
       </c>
-      <c r="M51" s="13">
+      <c r="M51">
         <v>1.0389999999999999</v>
       </c>
-      <c r="N51" s="11">
+      <c r="N51">
         <v>2289.79</v>
       </c>
-      <c r="O51" s="11">
+      <c r="O51">
         <v>202.846</v>
       </c>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="11">
+      <c r="Q51">
         <v>0.1</v>
       </c>
-      <c r="R51" s="11">
+      <c r="R51">
         <v>0.66900000000000004</v>
       </c>
-      <c r="S51" s="13">
+      <c r="S51">
         <v>0.64</v>
       </c>
-      <c r="T51" s="11">
+      <c r="T51">
         <v>6532.72</v>
       </c>
-      <c r="U51" s="11">
+      <c r="U51">
         <v>143.94300000000001</v>
       </c>
-      <c r="V51" s="11"/>
-      <c r="W51" s="11">
+      <c r="W51">
         <v>0.20100000000000001</v>
       </c>
-      <c r="X51" s="11">
+      <c r="X51">
         <v>6.3E-2</v>
       </c>
-      <c r="Y51" s="11">
+      <c r="Y51">
         <v>1.8320000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="1">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A52">
         <v>2021</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52">
         <v>21848.15</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52">
         <v>158.87799999999999</v>
       </c>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11">
+      <c r="E52">
         <v>0.25700000000000001</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52">
         <v>0.22700000000000001</v>
       </c>
-      <c r="G52" s="13">
+      <c r="G52">
         <v>0.69099999999999995</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52">
         <v>13124.6</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52">
         <v>153.63399999999999</v>
       </c>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11">
+      <c r="K52">
         <v>0.251</v>
       </c>
-      <c r="L52" s="11">
+      <c r="L52">
         <v>0.153</v>
       </c>
-      <c r="M52" s="13">
+      <c r="M52">
         <v>1.05</v>
       </c>
-      <c r="N52" s="11">
+      <c r="N52">
         <v>1985.26</v>
       </c>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
-      <c r="R52" s="11"/>
-      <c r="S52" s="13">
+      <c r="S52">
         <v>0.77</v>
       </c>
-      <c r="T52" s="11">
+      <c r="T52">
         <v>6738.29</v>
       </c>
-      <c r="U52" s="11">
+      <c r="U52">
         <v>164.12200000000001</v>
       </c>
-      <c r="V52" s="11"/>
-      <c r="W52" s="11">
+      <c r="W52">
         <v>0.26200000000000001</v>
       </c>
-      <c r="X52" s="11">
+      <c r="X52">
         <v>0.30099999999999999</v>
       </c>
-      <c r="Y52" s="11">
+      <c r="Y52">
         <v>1.978</v>
       </c>
     </row>

--- a/Indicator_4/Real_data/Blue_Shark_NAtl.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_NAtl.xlsx
@@ -1,300 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AB8CB0-0A53-4770-98CC-D819B8557402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Blue_Shark_NAtl</t>
-  </si>
-  <si>
-    <t>E.g. 'Swordfish_Natl'</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>max_age</t>
-  </si>
-  <si>
-    <t>15.18</t>
-  </si>
-  <si>
-    <t>Age to 5% natural survival</t>
-  </si>
-  <si>
-    <t>Life history</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>0.107</t>
-  </si>
-  <si>
-    <t>von Bertalannfy K</t>
-  </si>
-  <si>
-    <t>Linf</t>
-  </si>
-  <si>
-    <t>0.576</t>
-  </si>
-  <si>
-    <t>von Bertalannfy L-infinity (asymptotic length)</t>
-  </si>
-  <si>
-    <t>L50_Linf</t>
-  </si>
-  <si>
-    <t>337.3</t>
-  </si>
-  <si>
-    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>0.394</t>
-  </si>
-  <si>
-    <t>Length at 5% selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Fleet selectivity</t>
-  </si>
-  <si>
-    <t>All fleets combined</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.881</t>
-  </si>
-  <si>
-    <t>Length at full selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
-  </si>
-  <si>
-    <t>0.468</t>
-  </si>
-  <si>
-    <t>Selectivity of maximum length class</t>
-  </si>
-  <si>
-    <t>Fleet_1_L5_L50</t>
-  </si>
-  <si>
-    <t>0.391</t>
-  </si>
-  <si>
-    <t>Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet_1_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.532</t>
-  </si>
-  <si>
-    <t>Fleet_1_VML</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>Fleet_2_L5_L50</t>
-  </si>
-  <si>
-    <t>0.498</t>
-  </si>
-  <si>
-    <t>Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_2_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.837</t>
-  </si>
-  <si>
-    <t>Fleet_2_VML</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Fleet_3_L5_L50</t>
-  </si>
-  <si>
-    <t>0.479</t>
-  </si>
-  <si>
-    <t>Fleet 3</t>
-  </si>
-  <si>
-    <t>Fleet_3_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.042</t>
-  </si>
-  <si>
-    <t>Fleet_3_VML</t>
-  </si>
-  <si>
-    <t>0.999</t>
-  </si>
-  <si>
-    <t>Fleet_1_CF</t>
-  </si>
-  <si>
-    <t>0.727</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet catch scale</t>
-  </si>
-  <si>
-    <t>Fleet_2_CF</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_3_CF</t>
-  </si>
-  <si>
-    <t>0.169</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 3</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total_catch</t>
-  </si>
-  <si>
-    <t>Total_mean_len</t>
-  </si>
-  <si>
-    <t>Total_mean_age</t>
-  </si>
-  <si>
-    <t>Total_CV_len</t>
-  </si>
-  <si>
-    <t>Total_frac_mat</t>
-  </si>
-  <si>
-    <t>Total_Index</t>
-  </si>
-  <si>
-    <t>Fleet_1_catch</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_1_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_1_Index</t>
-  </si>
-  <si>
-    <t>Fleet_2_catch</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_2_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_2_Index</t>
-  </si>
-  <si>
-    <t>Fleet_3_catch</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_3_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_3_Index</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -394,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -428,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -463,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -639,365 +351,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Blue_Shark_NAtl</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E.g. 'Swordfish_Natl'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_age</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15.18</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age to 5% natural survival</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>von Bertalannfy K</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>von Bertalannfy L-infinity (asymptotic length)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L50_Linf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>337.3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total_L5_L50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.394</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total_VML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.468</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fleet_1_L5_L50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.391</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fleet_1_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.532</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet_1_VML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fleet_2_L5_L50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.498</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet_2_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fleet_2_VML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet_3_L5_L50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.479</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fleet_3_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.042</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fleet_3_VML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.999</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fleet_1_CF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.727</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fleet_2_CF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fleet_3_CF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.169</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1006,88 +928,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_catch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_len</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total_CV_len</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_frac_mat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_len</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_age</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_CV_len</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_frac_mat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_Index</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_catch</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_len</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_age</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_CV_len</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_frac_mat</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_Index</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_catch</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_len</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_age</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_CV_len</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_frac_mat</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1971</v>
       </c>
@@ -1101,13 +1073,13 @@
         <v>14085.2</v>
       </c>
       <c r="N2">
-        <v>1257.8699999999999</v>
+        <v>1257.87</v>
       </c>
       <c r="T2">
         <v>737.79</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>1972</v>
       </c>
@@ -1127,12 +1099,12 @@
         <v>932.29</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>1973</v>
       </c>
       <c r="B4">
-        <v>17508.810000000001</v>
+        <v>17508.81</v>
       </c>
       <c r="G4">
         <v>1.488</v>
@@ -1144,10 +1116,10 @@
         <v>653.64</v>
       </c>
       <c r="T4">
-        <v>901.07</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+        <v>901.0700000000001</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>1974</v>
       </c>
@@ -1155,7 +1127,7 @@
         <v>16205.45</v>
       </c>
       <c r="G5">
-        <v>1.4930000000000001</v>
+        <v>1.493</v>
       </c>
       <c r="H5">
         <v>12041.5</v>
@@ -1167,7 +1139,7 @@
         <v>741.97</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6">
         <v>1975</v>
       </c>
@@ -1187,7 +1159,7 @@
         <v>674.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7">
         <v>1976</v>
       </c>
@@ -1195,7 +1167,7 @@
         <v>13662.85</v>
       </c>
       <c r="G7">
-        <v>1.4990000000000001</v>
+        <v>1.499</v>
       </c>
       <c r="H7">
         <v>11721</v>
@@ -1207,7 +1179,7 @@
         <v>811.84</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>1977</v>
       </c>
@@ -1215,7 +1187,7 @@
         <v>17895.96</v>
       </c>
       <c r="G8">
-        <v>1.4990000000000001</v>
+        <v>1.499</v>
       </c>
       <c r="H8">
         <v>13773.1</v>
@@ -1227,7 +1199,7 @@
         <v>827.84</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9">
         <v>1978</v>
       </c>
@@ -1247,7 +1219,7 @@
         <v>2492.61</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>1979</v>
       </c>
@@ -1255,7 +1227,7 @@
         <v>14636.6</v>
       </c>
       <c r="G10">
-        <v>1.5109999999999999</v>
+        <v>1.511</v>
       </c>
       <c r="H10">
         <v>10747.1</v>
@@ -1267,7 +1239,7 @@
         <v>2965.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11">
         <v>1980</v>
       </c>
@@ -1275,7 +1247,7 @@
         <v>22781.96</v>
       </c>
       <c r="G11">
-        <v>1.5269999999999999</v>
+        <v>1.527</v>
       </c>
       <c r="H11">
         <v>15858.4</v>
@@ -1287,7 +1259,7 @@
         <v>2021.07</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12">
         <v>1981</v>
       </c>
@@ -1307,7 +1279,7 @@
         <v>1029.2</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13">
         <v>1982</v>
       </c>
@@ -1315,10 +1287,10 @@
         <v>25741.59</v>
       </c>
       <c r="G13">
-        <v>1.5629999999999999</v>
+        <v>1.563</v>
       </c>
       <c r="H13">
-        <v>18955.099999999999</v>
+        <v>18955.1</v>
       </c>
       <c r="N13">
         <v>5331.14</v>
@@ -1327,7 +1299,7 @@
         <v>1455.35</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14">
         <v>1983</v>
       </c>
@@ -1335,7 +1307,7 @@
         <v>35273.08</v>
       </c>
       <c r="G14">
-        <v>1.5609999999999999</v>
+        <v>1.561</v>
       </c>
       <c r="H14">
         <v>29552.3</v>
@@ -1347,7 +1319,7 @@
         <v>2260.11</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15">
         <v>1984</v>
       </c>
@@ -1361,21 +1333,21 @@
         <v>26285</v>
       </c>
       <c r="N15">
-        <v>2455.0100000000002</v>
+        <v>2455.01</v>
       </c>
       <c r="T15">
         <v>1472.66</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16">
         <v>1985</v>
       </c>
       <c r="B16">
-        <v>36307.839999999997</v>
+        <v>36307.84</v>
       </c>
       <c r="G16">
-        <v>1.5289999999999999</v>
+        <v>1.529</v>
       </c>
       <c r="H16">
         <v>30930.1</v>
@@ -1387,7 +1359,7 @@
         <v>1727.4</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17">
         <v>1986</v>
       </c>
@@ -1395,10 +1367,10 @@
         <v>47885.36</v>
       </c>
       <c r="G17">
-        <v>1.4930000000000001</v>
+        <v>1.493</v>
       </c>
       <c r="H17">
-        <v>40424.300000000003</v>
+        <v>40424.3</v>
       </c>
       <c r="N17">
         <v>2928.4</v>
@@ -1407,7 +1379,7 @@
         <v>4532.66</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18">
         <v>1987</v>
       </c>
@@ -1427,7 +1399,7 @@
         <v>6164.96</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19">
         <v>1988</v>
       </c>
@@ -1435,7 +1407,7 @@
         <v>46984.9</v>
       </c>
       <c r="G19">
-        <v>1.4179999999999999</v>
+        <v>1.418</v>
       </c>
       <c r="H19">
         <v>39958.1</v>
@@ -1444,10 +1416,10 @@
         <v>2388.19</v>
       </c>
       <c r="T19">
-        <v>4638.6099999999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+        <v>4638.61</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1989</v>
       </c>
@@ -1455,7 +1427,7 @@
         <v>31439.73</v>
       </c>
       <c r="G20">
-        <v>1.3420000000000001</v>
+        <v>1.342</v>
       </c>
       <c r="H20">
         <v>23708.5</v>
@@ -1467,7 +1439,7 @@
         <v>3198.53</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21">
         <v>1990</v>
       </c>
@@ -1475,7 +1447,7 @@
         <v>31685.66</v>
       </c>
       <c r="G21">
-        <v>1.2410000000000001</v>
+        <v>1.241</v>
       </c>
       <c r="H21">
         <v>23875</v>
@@ -1484,18 +1456,18 @@
         <v>3599.22</v>
       </c>
       <c r="T21">
-        <v>4211.4399999999996</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+        <v>4211.44</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>1991</v>
       </c>
       <c r="B22">
-        <v>37640.879999999997</v>
+        <v>37640.88</v>
       </c>
       <c r="G22">
-        <v>1.1519999999999999</v>
+        <v>1.152</v>
       </c>
       <c r="H22">
         <v>27080</v>
@@ -1507,7 +1479,7 @@
         <v>6981.28</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23">
         <v>1992</v>
       </c>
@@ -1515,10 +1487,10 @@
         <v>36529.01</v>
       </c>
       <c r="G23">
-        <v>1.0920000000000001</v>
+        <v>1.092</v>
       </c>
       <c r="H23">
-        <v>26434.799999999999</v>
+        <v>26434.8</v>
       </c>
       <c r="N23">
         <v>4509.07</v>
@@ -1527,10 +1499,10 @@
         <v>5585.14</v>
       </c>
       <c r="Y23">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -1544,7 +1516,7 @@
         <v>0.24</v>
       </c>
       <c r="F24">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="G24">
         <v>1.036</v>
@@ -1565,24 +1537,24 @@
         <v>0.24</v>
       </c>
       <c r="X24">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="Y24">
         <v>0.115</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25">
         <v>1994</v>
       </c>
       <c r="B25">
-        <v>37242.050000000003</v>
+        <v>37242.05</v>
       </c>
       <c r="C25">
         <v>120.754</v>
       </c>
       <c r="E25">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="F25">
         <v>0.02</v>
@@ -1606,16 +1578,16 @@
         <v>120.754</v>
       </c>
       <c r="W25">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="X25">
         <v>0.02</v>
       </c>
       <c r="Y25">
-        <v>4.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1995</v>
       </c>
@@ -1626,13 +1598,13 @@
         <v>133.143</v>
       </c>
       <c r="E26">
-        <v>0.28699999999999998</v>
+        <v>0.287</v>
       </c>
       <c r="F26">
-        <v>7.0999999999999994E-2</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G26">
-        <v>0.91600000000000004</v>
+        <v>0.916</v>
       </c>
       <c r="H26">
         <v>28919.7</v>
@@ -1650,24 +1622,24 @@
         <v>133.143</v>
       </c>
       <c r="W26">
-        <v>0.28699999999999998</v>
+        <v>0.287</v>
       </c>
       <c r="X26">
-        <v>7.0999999999999994E-2</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y26">
-        <v>4.9000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1996</v>
       </c>
       <c r="B27">
-        <v>35865.919999999998</v>
+        <v>35865.92</v>
       </c>
       <c r="G27">
-        <v>0.84799999999999998</v>
+        <v>0.848</v>
       </c>
       <c r="H27">
         <v>22971.8</v>
@@ -1679,13 +1651,13 @@
         <v>1.01</v>
       </c>
       <c r="T27">
-        <v>8714.86</v>
+        <v>8714.860000000001</v>
       </c>
       <c r="Y27">
-        <v>3.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>1997</v>
       </c>
@@ -1693,16 +1665,16 @@
         <v>34284.99</v>
       </c>
       <c r="C28">
-        <v>153.69300000000001</v>
+        <v>153.693</v>
       </c>
       <c r="E28">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="F28">
         <v>0.224</v>
       </c>
       <c r="G28">
-        <v>0.79500000000000004</v>
+        <v>0.795</v>
       </c>
       <c r="H28">
         <v>24497.4</v>
@@ -1714,22 +1686,22 @@
         <v>0.309</v>
       </c>
       <c r="L28">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="M28">
-        <v>0.74299999999999999</v>
+        <v>0.743</v>
       </c>
       <c r="N28">
         <v>4191.43</v>
       </c>
       <c r="O28">
-        <v>178.42699999999999</v>
+        <v>178.427</v>
       </c>
       <c r="Q28">
-        <v>0.20200000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="R28">
-        <v>0.35199999999999998</v>
+        <v>0.352</v>
       </c>
       <c r="S28">
         <v>1.06</v>
@@ -1738,19 +1710,19 @@
         <v>5596.16</v>
       </c>
       <c r="U28">
-        <v>150.28899999999999</v>
+        <v>150.289</v>
       </c>
       <c r="W28">
         <v>0.315</v>
       </c>
       <c r="X28">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="Y28">
-        <v>0.66300000000000003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.663</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1998</v>
       </c>
@@ -1758,43 +1730,43 @@
         <v>30604.34</v>
       </c>
       <c r="C29">
-        <v>178.17500000000001</v>
+        <v>178.175</v>
       </c>
       <c r="E29">
         <v>0.223</v>
       </c>
       <c r="F29">
-        <v>0.38500000000000001</v>
+        <v>0.385</v>
       </c>
       <c r="G29">
-        <v>0.72499999999999998</v>
+        <v>0.725</v>
       </c>
       <c r="H29">
         <v>22504.3</v>
       </c>
       <c r="I29">
-        <v>148.95400000000001</v>
+        <v>148.954</v>
       </c>
       <c r="K29">
-        <v>0.29199999999999998</v>
+        <v>0.292</v>
       </c>
       <c r="L29">
         <v>0.189</v>
       </c>
       <c r="M29">
-        <v>0.71899999999999997</v>
+        <v>0.719</v>
       </c>
       <c r="N29">
         <v>3460.87</v>
       </c>
       <c r="O29">
-        <v>182.91900000000001</v>
+        <v>182.919</v>
       </c>
       <c r="Q29">
         <v>0.18</v>
       </c>
       <c r="R29">
-        <v>0.35399999999999998</v>
+        <v>0.354</v>
       </c>
       <c r="S29">
         <v>0.93</v>
@@ -1803,19 +1775,19 @@
         <v>4639.17</v>
       </c>
       <c r="U29">
-        <v>202.65299999999999</v>
+        <v>202.653</v>
       </c>
       <c r="W29">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="X29">
-        <v>0.61199999999999999</v>
+        <v>0.612</v>
       </c>
       <c r="Y29">
-        <v>0.68400000000000005</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.6840000000000001</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>1999</v>
       </c>
@@ -1832,7 +1804,7 @@
         <v>0.36</v>
       </c>
       <c r="G30">
-        <v>0.65400000000000003</v>
+        <v>0.654</v>
       </c>
       <c r="H30">
         <v>21811.3</v>
@@ -1841,13 +1813,13 @@
         <v>142.91</v>
       </c>
       <c r="K30">
-        <v>0.26800000000000002</v>
+        <v>0.268</v>
       </c>
       <c r="L30">
         <v>0.126</v>
       </c>
       <c r="M30">
-        <v>0.84499999999999997</v>
+        <v>0.845</v>
       </c>
       <c r="N30">
         <v>3149.59</v>
@@ -1859,36 +1831,36 @@
         <v>0.107</v>
       </c>
       <c r="R30">
-        <v>0.59399999999999997</v>
+        <v>0.594</v>
       </c>
       <c r="S30">
         <v>0.64</v>
       </c>
       <c r="T30">
-        <v>4924.6400000000003</v>
+        <v>4924.64</v>
       </c>
       <c r="Y30">
-        <v>0.56799999999999995</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.5679999999999999</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>2000</v>
       </c>
       <c r="B31">
-        <v>31866.959999999999</v>
+        <v>31866.96</v>
       </c>
       <c r="C31">
         <v>158.434</v>
       </c>
       <c r="E31">
-        <v>0.27700000000000002</v>
+        <v>0.277</v>
       </c>
       <c r="F31">
-        <v>0.24199999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="G31">
-        <v>0.61199999999999999</v>
+        <v>0.612</v>
       </c>
       <c r="H31">
         <v>24111.9</v>
@@ -1897,7 +1869,7 @@
         <v>138.334</v>
       </c>
       <c r="K31">
-        <v>0.29899999999999999</v>
+        <v>0.299</v>
       </c>
       <c r="L31">
         <v>0.106</v>
@@ -1909,7 +1881,7 @@
         <v>2838.4</v>
       </c>
       <c r="O31">
-        <v>178.53399999999999</v>
+        <v>178.534</v>
       </c>
       <c r="Q31">
         <v>0.255</v>
@@ -1924,33 +1896,33 @@
         <v>4916.66</v>
       </c>
       <c r="Y31">
-        <v>0.75900000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.759</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>2001</v>
       </c>
       <c r="B32">
-        <v>25045.040000000001</v>
+        <v>25045.04</v>
       </c>
       <c r="C32">
-        <v>147.62200000000001</v>
+        <v>147.622</v>
       </c>
       <c r="E32">
-        <v>0.25800000000000001</v>
+        <v>0.258</v>
       </c>
       <c r="F32">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="G32">
-        <v>0.58899999999999997</v>
+        <v>0.589</v>
       </c>
       <c r="H32">
         <v>17361.7</v>
       </c>
       <c r="I32">
-        <v>136.54599999999999</v>
+        <v>136.546</v>
       </c>
       <c r="K32">
         <v>0.31</v>
@@ -1959,7 +1931,7 @@
         <v>0.111</v>
       </c>
       <c r="M32">
-        <v>1.0329999999999999</v>
+        <v>1.033</v>
       </c>
       <c r="N32">
         <v>2723.72</v>
@@ -1968,7 +1940,7 @@
         <v>158.697</v>
       </c>
       <c r="Q32">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="R32">
         <v>0.127</v>
@@ -1980,10 +1952,10 @@
         <v>4959.62</v>
       </c>
       <c r="Y32">
-        <v>0.84199999999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.842</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>2002</v>
       </c>
@@ -1994,13 +1966,13 @@
         <v>145.655</v>
       </c>
       <c r="E33">
-        <v>0.22800000000000001</v>
+        <v>0.228</v>
       </c>
       <c r="F33">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="G33">
-        <v>0.56200000000000006</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H33">
         <v>15665.9</v>
@@ -2009,13 +1981,13 @@
         <v>139.012</v>
       </c>
       <c r="K33">
-        <v>0.25600000000000001</v>
+        <v>0.256</v>
       </c>
       <c r="L33">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="M33">
-        <v>0.88800000000000001</v>
+        <v>0.888</v>
       </c>
       <c r="N33">
         <v>1890.03</v>
@@ -2027,19 +1999,19 @@
         <v>0.2</v>
       </c>
       <c r="R33">
-        <v>6.9000000000000006E-2</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S33">
         <v>0.53</v>
       </c>
       <c r="T33">
-        <v>5186.2299999999996</v>
+        <v>5186.23</v>
       </c>
       <c r="Y33">
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34">
         <v>2003</v>
       </c>
@@ -2047,43 +2019,43 @@
         <v>26860.53</v>
       </c>
       <c r="C34">
-        <v>156.98500000000001</v>
+        <v>156.985</v>
       </c>
       <c r="E34">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="F34">
-        <v>0.13100000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="G34">
-        <v>0.52900000000000003</v>
+        <v>0.529</v>
       </c>
       <c r="H34">
         <v>15974.5</v>
       </c>
       <c r="I34">
-        <v>146.36199999999999</v>
+        <v>146.362</v>
       </c>
       <c r="K34">
-        <v>0.27200000000000002</v>
+        <v>0.272</v>
       </c>
       <c r="L34">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="M34">
-        <v>1.0309999999999999</v>
+        <v>1.031</v>
       </c>
       <c r="N34">
         <v>3097.72</v>
       </c>
       <c r="O34">
-        <v>153.09800000000001</v>
+        <v>153.098</v>
       </c>
       <c r="Q34">
-        <v>0.16900000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="R34">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="S34">
         <v>0.77</v>
@@ -2092,19 +2064,19 @@
         <v>7788.31</v>
       </c>
       <c r="U34">
-        <v>171.49600000000001</v>
+        <v>171.496</v>
       </c>
       <c r="W34">
-        <v>0.23799999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="X34">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="Y34">
-        <v>0.89300000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.893</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>2004</v>
       </c>
@@ -2124,16 +2096,16 @@
         <v>0.503</v>
       </c>
       <c r="H35">
-        <v>17313.900000000001</v>
+        <v>17313.9</v>
       </c>
       <c r="I35">
-        <v>147.11099999999999</v>
+        <v>147.111</v>
       </c>
       <c r="K35">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="L35">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="M35">
         <v>0.93</v>
@@ -2142,13 +2114,13 @@
         <v>3194.83</v>
       </c>
       <c r="O35">
-        <v>148.96199999999999</v>
+        <v>148.962</v>
       </c>
       <c r="Q35">
-        <v>0.19800000000000001</v>
+        <v>0.198</v>
       </c>
       <c r="R35">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="S35">
         <v>0.53</v>
@@ -2157,19 +2129,19 @@
         <v>4756.82</v>
       </c>
       <c r="U35">
-        <v>156.80000000000001</v>
+        <v>156.8</v>
       </c>
       <c r="W35">
-        <v>0.26900000000000002</v>
+        <v>0.269</v>
       </c>
       <c r="X35">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="Y35">
         <v>1.036</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36">
         <v>2005</v>
       </c>
@@ -2180,7 +2152,7 @@
         <v>150.547</v>
       </c>
       <c r="E36">
-        <v>0.22900000000000001</v>
+        <v>0.229</v>
       </c>
       <c r="F36">
         <v>0.112</v>
@@ -2192,49 +2164,49 @@
         <v>15006.1</v>
       </c>
       <c r="I36">
-        <v>136.94499999999999</v>
+        <v>136.945</v>
       </c>
       <c r="K36">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="L36">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="M36">
-        <v>0.89100000000000001</v>
+        <v>0.891</v>
       </c>
       <c r="N36">
         <v>3530.98</v>
       </c>
       <c r="O36">
-        <v>143.38399999999999</v>
+        <v>143.384</v>
       </c>
       <c r="Q36">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="R36">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="S36">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T36">
         <v>6472.37</v>
       </c>
       <c r="U36">
-        <v>171.31100000000001</v>
+        <v>171.311</v>
       </c>
       <c r="W36">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="X36">
-        <v>0.22600000000000001</v>
+        <v>0.226</v>
       </c>
       <c r="Y36">
-        <v>0.84499999999999997</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.845</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>2006</v>
       </c>
@@ -2242,7 +2214,7 @@
         <v>24639.3</v>
       </c>
       <c r="C37">
-        <v>160.55799999999999</v>
+        <v>160.558</v>
       </c>
       <c r="E37">
         <v>0.223</v>
@@ -2251,34 +2223,34 @@
         <v>0.26</v>
       </c>
       <c r="G37">
-        <v>0.47399999999999998</v>
+        <v>0.474</v>
       </c>
       <c r="H37">
         <v>15463.6</v>
       </c>
       <c r="I37">
-        <v>145.04599999999999</v>
+        <v>145.046</v>
       </c>
       <c r="K37">
         <v>0.31</v>
       </c>
       <c r="L37">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="M37">
-        <v>0.88400000000000001</v>
+        <v>0.884</v>
       </c>
       <c r="N37">
         <v>2824.18</v>
       </c>
       <c r="O37">
-        <v>139.65100000000001</v>
+        <v>139.651</v>
       </c>
       <c r="Q37">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="R37">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="S37">
         <v>0.87</v>
@@ -2293,13 +2265,13 @@
         <v>0.121</v>
       </c>
       <c r="X37">
-        <v>0.55800000000000005</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="Y37">
-        <v>0.82799999999999996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.828</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38">
         <v>2007</v>
       </c>
@@ -2307,43 +2279,43 @@
         <v>27276.78</v>
       </c>
       <c r="C38">
-        <v>136.46299999999999</v>
+        <v>136.463</v>
       </c>
       <c r="E38">
         <v>0.24</v>
       </c>
       <c r="F38">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="G38">
-        <v>0.47499999999999998</v>
+        <v>0.475</v>
       </c>
       <c r="H38">
         <v>17038.5</v>
       </c>
       <c r="I38">
-        <v>130.17699999999999</v>
+        <v>130.177</v>
       </c>
       <c r="K38">
-        <v>0.28799999999999998</v>
+        <v>0.288</v>
       </c>
       <c r="L38">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="M38">
         <v>0.998</v>
       </c>
       <c r="N38">
-        <v>2270.9899999999998</v>
+        <v>2270.99</v>
       </c>
       <c r="O38">
-        <v>150.65899999999999</v>
+        <v>150.659</v>
       </c>
       <c r="Q38">
         <v>0.223</v>
       </c>
       <c r="R38">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S38">
         <v>1.02</v>
@@ -2355,33 +2327,33 @@
         <v>128.554</v>
       </c>
       <c r="W38">
-        <v>0.21099999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="X38">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="Y38">
-        <v>0.69399999999999995</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.694</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>2008</v>
       </c>
       <c r="B39">
-        <v>31378.959999999999</v>
+        <v>31378.96</v>
       </c>
       <c r="C39">
-        <v>158.57599999999999</v>
+        <v>158.576</v>
       </c>
       <c r="E39">
-        <v>0.23200000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="F39">
-        <v>0.26100000000000001</v>
+        <v>0.261</v>
       </c>
       <c r="G39">
-        <v>0.48099999999999998</v>
+        <v>0.481</v>
       </c>
       <c r="H39">
         <v>20787.8</v>
@@ -2390,22 +2362,22 @@
         <v>145.666</v>
       </c>
       <c r="K39">
-        <v>0.30299999999999999</v>
+        <v>0.303</v>
       </c>
       <c r="L39">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="M39">
-        <v>1.1539999999999999</v>
+        <v>1.154</v>
       </c>
       <c r="N39">
         <v>3186.59</v>
       </c>
       <c r="O39">
-        <v>154.95599999999999</v>
+        <v>154.956</v>
       </c>
       <c r="Q39">
-        <v>0.23300000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="R39">
         <v>0.122</v>
@@ -2420,7 +2392,7 @@
         <v>166.84</v>
       </c>
       <c r="W39">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="X39">
         <v>0.39</v>
@@ -2429,7 +2401,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40">
         <v>2009</v>
       </c>
@@ -2452,13 +2424,13 @@
         <v>24465.5</v>
       </c>
       <c r="I40">
-        <v>154.66399999999999</v>
+        <v>154.664</v>
       </c>
       <c r="K40">
-        <v>0.30499999999999999</v>
+        <v>0.305</v>
       </c>
       <c r="L40">
-        <v>0.22500000000000001</v>
+        <v>0.225</v>
       </c>
       <c r="M40">
         <v>1.095</v>
@@ -2470,7 +2442,7 @@
         <v>169.874</v>
       </c>
       <c r="Q40">
-        <v>0.20899999999999999</v>
+        <v>0.209</v>
       </c>
       <c r="R40">
         <v>0.24</v>
@@ -2479,7 +2451,7 @@
         <v>1.24</v>
       </c>
       <c r="T40">
-        <v>8727.19</v>
+        <v>8727.190000000001</v>
       </c>
       <c r="U40">
         <v>214.03</v>
@@ -2488,13 +2460,13 @@
         <v>0.129</v>
       </c>
       <c r="X40">
-        <v>0.77700000000000002</v>
+        <v>0.777</v>
       </c>
       <c r="Y40">
-        <v>0.68700000000000006</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.6870000000000001</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>2010</v>
       </c>
@@ -2502,16 +2474,16 @@
         <v>38171.74</v>
       </c>
       <c r="C41">
-        <v>160.71700000000001</v>
+        <v>160.717</v>
       </c>
       <c r="E41">
         <v>0.215</v>
       </c>
       <c r="F41">
-        <v>0.29699999999999999</v>
+        <v>0.297</v>
       </c>
       <c r="G41">
-        <v>0.49199999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="H41">
         <v>26094.3</v>
@@ -2538,7 +2510,7 @@
         <v>0.185</v>
       </c>
       <c r="R41">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="S41">
         <v>1.44</v>
@@ -2547,24 +2519,24 @@
         <v>9322.4</v>
       </c>
       <c r="U41">
-        <v>164.18899999999999</v>
+        <v>164.189</v>
       </c>
       <c r="W41">
         <v>0.192</v>
       </c>
       <c r="X41">
-        <v>0.39800000000000002</v>
+        <v>0.398</v>
       </c>
       <c r="Y41">
-        <v>0.86299999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.863</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>2011</v>
       </c>
       <c r="B42">
-        <v>39006.980000000003</v>
+        <v>39006.98</v>
       </c>
       <c r="C42">
         <v>171.11</v>
@@ -2573,7 +2545,7 @@
         <v>0.184</v>
       </c>
       <c r="F42">
-        <v>0.36199999999999999</v>
+        <v>0.362</v>
       </c>
       <c r="G42">
         <v>0.499</v>
@@ -2582,49 +2554,49 @@
         <v>27988.2</v>
       </c>
       <c r="I42">
-        <v>134.45500000000001</v>
+        <v>134.455</v>
       </c>
       <c r="K42">
         <v>0.309</v>
       </c>
       <c r="L42">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M42">
-        <v>1.1140000000000001</v>
+        <v>1.114</v>
       </c>
       <c r="N42">
         <v>2147.89</v>
       </c>
       <c r="O42">
-        <v>188.97900000000001</v>
+        <v>188.979</v>
       </c>
       <c r="Q42">
-        <v>0.16200000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="R42">
-        <v>0.44700000000000001</v>
+        <v>0.447</v>
       </c>
       <c r="S42">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T42">
-        <v>8870.89</v>
+        <v>8870.889999999999</v>
       </c>
       <c r="U42">
-        <v>175.80600000000001</v>
+        <v>175.806</v>
       </c>
       <c r="W42">
         <v>0.158</v>
       </c>
       <c r="X42">
-        <v>0.40500000000000003</v>
+        <v>0.405</v>
       </c>
       <c r="Y42">
         <v>1.129</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43">
         <v>2012</v>
       </c>
@@ -2638,10 +2610,10 @@
         <v>0.22</v>
       </c>
       <c r="F43">
-        <v>0.34100000000000003</v>
+        <v>0.341</v>
       </c>
       <c r="G43">
-        <v>0.51500000000000001</v>
+        <v>0.515</v>
       </c>
       <c r="H43">
         <v>28665.8</v>
@@ -2650,22 +2622,22 @@
         <v>136.083</v>
       </c>
       <c r="K43">
-        <v>0.27800000000000002</v>
+        <v>0.278</v>
       </c>
       <c r="L43">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M43">
-        <v>1.0960000000000001</v>
+        <v>1.096</v>
       </c>
       <c r="N43">
         <v>2256.35</v>
       </c>
       <c r="O43">
-        <v>163.05699999999999</v>
+        <v>163.057</v>
       </c>
       <c r="Q43">
-        <v>0.25600000000000001</v>
+        <v>0.256</v>
       </c>
       <c r="R43">
         <v>0.251</v>
@@ -2677,19 +2649,19 @@
         <v>5682.66</v>
       </c>
       <c r="U43">
-        <v>183.68799999999999</v>
+        <v>183.688</v>
       </c>
       <c r="W43">
         <v>0.189</v>
       </c>
       <c r="X43">
-        <v>0.45400000000000001</v>
+        <v>0.454</v>
       </c>
       <c r="Y43">
         <v>1.298</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44">
         <v>2013</v>
       </c>
@@ -2700,25 +2672,25 @@
         <v>166.714</v>
       </c>
       <c r="E44">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="F44">
-        <v>0.27800000000000002</v>
+        <v>0.278</v>
       </c>
       <c r="G44">
-        <v>0.54200000000000004</v>
+        <v>0.542</v>
       </c>
       <c r="H44">
         <v>28562</v>
       </c>
       <c r="I44">
-        <v>132.26499999999999</v>
+        <v>132.265</v>
       </c>
       <c r="K44">
-        <v>0.29099999999999998</v>
+        <v>0.291</v>
       </c>
       <c r="L44">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="M44">
         <v>1.149</v>
@@ -2730,7 +2702,7 @@
         <v>186.846</v>
       </c>
       <c r="Q44">
-        <v>0.16900000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="R44">
         <v>0.433</v>
@@ -2742,19 +2714,19 @@
         <v>6832.17</v>
       </c>
       <c r="U44">
-        <v>173.87200000000001</v>
+        <v>173.872</v>
       </c>
       <c r="W44">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="X44">
-        <v>0.29899999999999999</v>
+        <v>0.299</v>
       </c>
       <c r="Y44">
-        <v>1.1060000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.106</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>2014</v>
       </c>
@@ -2762,28 +2734,28 @@
         <v>38133.19</v>
       </c>
       <c r="C45">
-        <v>174.81100000000001</v>
+        <v>174.811</v>
       </c>
       <c r="E45">
-        <v>0.20200000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="F45">
-        <v>0.38600000000000001</v>
+        <v>0.386</v>
       </c>
       <c r="G45">
-        <v>0.57299999999999995</v>
+        <v>0.573</v>
       </c>
       <c r="H45">
         <v>29041.1</v>
       </c>
       <c r="I45">
-        <v>128.87700000000001</v>
+        <v>128.877</v>
       </c>
       <c r="K45">
-        <v>0.30199999999999999</v>
+        <v>0.302</v>
       </c>
       <c r="L45">
-        <v>8.6999999999999994E-2</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M45">
         <v>1.085</v>
@@ -2795,7 +2767,7 @@
         <v>185.571</v>
       </c>
       <c r="Q45">
-        <v>0.16800000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="R45">
         <v>0.441</v>
@@ -2810,60 +2782,60 @@
         <v>192.398</v>
       </c>
       <c r="W45">
-        <v>0.16800000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="X45">
-        <v>0.50900000000000001</v>
+        <v>0.509</v>
       </c>
       <c r="Y45">
         <v>1.597</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46">
         <v>2015</v>
       </c>
       <c r="B46">
-        <v>40190.769999999997</v>
+        <v>40190.77</v>
       </c>
       <c r="C46">
-        <v>156.99299999999999</v>
+        <v>156.993</v>
       </c>
       <c r="E46">
         <v>0.221</v>
       </c>
       <c r="F46">
-        <v>0.19400000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="G46">
-        <v>0.58799999999999997</v>
+        <v>0.588</v>
       </c>
       <c r="H46">
         <v>30078.3</v>
       </c>
       <c r="I46">
-        <v>134.78899999999999</v>
+        <v>134.789</v>
       </c>
       <c r="K46">
         <v>0.254</v>
       </c>
       <c r="L46">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="M46">
-        <v>1.1240000000000001</v>
+        <v>1.124</v>
       </c>
       <c r="N46">
         <v>4011.13</v>
       </c>
       <c r="O46">
-        <v>175.64500000000001</v>
+        <v>175.645</v>
       </c>
       <c r="Q46">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="R46">
-        <v>0.32100000000000001</v>
+        <v>0.321</v>
       </c>
       <c r="S46">
         <v>1.37</v>
@@ -2872,19 +2844,19 @@
         <v>6101.34</v>
       </c>
       <c r="U46">
-        <v>160.54400000000001</v>
+        <v>160.544</v>
       </c>
       <c r="W46">
-        <v>0.22900000000000001</v>
+        <v>0.229</v>
       </c>
       <c r="X46">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="Y46">
         <v>1.984</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47">
         <v>2016</v>
       </c>
@@ -2895,13 +2867,13 @@
         <v>168.09</v>
       </c>
       <c r="E47">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="F47">
         <v>0.251</v>
       </c>
       <c r="G47">
-        <v>0.58699999999999997</v>
+        <v>0.587</v>
       </c>
       <c r="H47">
         <v>29018.7</v>
@@ -2910,7 +2882,7 @@
         <v>143</v>
       </c>
       <c r="K47">
-        <v>0.26700000000000002</v>
+        <v>0.267</v>
       </c>
       <c r="L47">
         <v>0.113</v>
@@ -2922,13 +2894,13 @@
         <v>4217.09</v>
       </c>
       <c r="O47">
-        <v>187.56399999999999</v>
+        <v>187.564</v>
       </c>
       <c r="Q47">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="R47">
-        <v>0.44800000000000001</v>
+        <v>0.448</v>
       </c>
       <c r="S47">
         <v>1.17</v>
@@ -2937,7 +2909,7 @@
         <v>10849.67</v>
       </c>
       <c r="U47">
-        <v>170.89699999999999</v>
+        <v>170.897</v>
       </c>
       <c r="W47">
         <v>0.186</v>
@@ -2946,75 +2918,75 @@
         <v>0.221</v>
       </c>
       <c r="Y47">
-        <v>2.2010000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.201</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>2017</v>
       </c>
       <c r="B48">
-        <v>40004.480000000003</v>
+        <v>40004.48</v>
       </c>
       <c r="C48">
-        <v>178.16900000000001</v>
+        <v>178.169</v>
       </c>
       <c r="E48">
-        <v>0.17899999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="F48">
-        <v>0.38400000000000001</v>
+        <v>0.384</v>
       </c>
       <c r="G48">
-        <v>0.60599999999999998</v>
+        <v>0.606</v>
       </c>
       <c r="H48">
         <v>27316.5</v>
       </c>
       <c r="I48">
-        <v>146.54400000000001</v>
+        <v>146.544</v>
       </c>
       <c r="K48">
-        <v>0.25700000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="L48">
         <v>0.125</v>
       </c>
       <c r="M48">
-        <v>0.97599999999999998</v>
+        <v>0.976</v>
       </c>
       <c r="N48">
-        <v>4443.8500000000004</v>
+        <v>4443.85</v>
       </c>
       <c r="O48">
         <v>189.34</v>
       </c>
       <c r="Q48">
-        <v>0.14699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="R48">
-        <v>0.45700000000000002</v>
+        <v>0.457</v>
       </c>
       <c r="S48">
-        <v>1.1299999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="T48">
-        <v>8244.1299999999992</v>
+        <v>8244.129999999999</v>
       </c>
       <c r="U48">
-        <v>188.39599999999999</v>
+        <v>188.396</v>
       </c>
       <c r="W48">
         <v>0.156</v>
       </c>
       <c r="X48">
-        <v>0.47799999999999998</v>
+        <v>0.478</v>
       </c>
       <c r="Y48">
         <v>1.964</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49">
         <v>2018</v>
       </c>
@@ -3022,7 +2994,7 @@
         <v>33978.71</v>
       </c>
       <c r="C49">
-        <v>168.21700000000001</v>
+        <v>168.217</v>
       </c>
       <c r="E49">
         <v>0.216</v>
@@ -3031,7 +3003,7 @@
         <v>0.309</v>
       </c>
       <c r="G49">
-        <v>0.64600000000000002</v>
+        <v>0.646</v>
       </c>
       <c r="H49">
         <v>21684.7</v>
@@ -3043,22 +3015,22 @@
         <v>0.252</v>
       </c>
       <c r="L49">
-        <v>7.0999999999999994E-2</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M49">
-        <v>0.96199999999999997</v>
+        <v>0.962</v>
       </c>
       <c r="N49">
         <v>4111.12</v>
       </c>
       <c r="O49">
-        <v>179.28800000000001</v>
+        <v>179.288</v>
       </c>
       <c r="Q49">
         <v>0.189</v>
       </c>
       <c r="R49">
-        <v>0.38500000000000001</v>
+        <v>0.385</v>
       </c>
       <c r="S49">
         <v>0.74</v>
@@ -3067,19 +3039,19 @@
         <v>8182.89</v>
       </c>
       <c r="U49">
-        <v>175.68700000000001</v>
+        <v>175.687</v>
       </c>
       <c r="W49">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="X49">
-        <v>0.36199999999999999</v>
+        <v>0.362</v>
       </c>
       <c r="Y49">
-        <v>1.7270000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.727</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -3090,13 +3062,13 @@
         <v>168.405</v>
       </c>
       <c r="E50">
-        <v>0.22800000000000001</v>
+        <v>0.228</v>
       </c>
       <c r="F50">
-        <v>0.32800000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="G50">
-        <v>0.66200000000000003</v>
+        <v>0.662</v>
       </c>
       <c r="H50">
         <v>16314.2</v>
@@ -3105,22 +3077,22 @@
         <v>134.149</v>
       </c>
       <c r="K50">
-        <v>0.28699999999999998</v>
+        <v>0.287</v>
       </c>
       <c r="L50">
         <v>0.09</v>
       </c>
       <c r="M50">
-        <v>0.95299999999999996</v>
+        <v>0.953</v>
       </c>
       <c r="N50">
         <v>3855.22</v>
       </c>
       <c r="O50">
-        <v>183.38800000000001</v>
+        <v>183.388</v>
       </c>
       <c r="Q50">
-        <v>0.19900000000000001</v>
+        <v>0.199</v>
       </c>
       <c r="R50">
         <v>0.46</v>
@@ -3135,16 +3107,16 @@
         <v>178.042</v>
       </c>
       <c r="W50">
-        <v>0.21199999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="X50">
-        <v>0.38100000000000001</v>
+        <v>0.381</v>
       </c>
       <c r="Y50">
-        <v>2.0870000000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.087</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>2020</v>
       </c>
@@ -3155,28 +3127,28 @@
         <v>167.97</v>
       </c>
       <c r="E51">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="F51">
-        <v>0.30499999999999999</v>
+        <v>0.305</v>
       </c>
       <c r="G51">
-        <v>0.67500000000000004</v>
+        <v>0.675</v>
       </c>
       <c r="H51">
         <v>12324.9</v>
       </c>
       <c r="I51">
-        <v>157.12100000000001</v>
+        <v>157.121</v>
       </c>
       <c r="K51">
-        <v>0.23300000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="L51">
         <v>0.183</v>
       </c>
       <c r="M51">
-        <v>1.0389999999999999</v>
+        <v>1.039</v>
       </c>
       <c r="N51">
         <v>2289.79</v>
@@ -3188,7 +3160,7 @@
         <v>0.1</v>
       </c>
       <c r="R51">
-        <v>0.66900000000000004</v>
+        <v>0.669</v>
       </c>
       <c r="S51">
         <v>0.64</v>
@@ -3197,19 +3169,19 @@
         <v>6532.72</v>
       </c>
       <c r="U51">
-        <v>143.94300000000001</v>
+        <v>143.943</v>
       </c>
       <c r="W51">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="X51">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="Y51">
-        <v>1.8320000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.832</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>2021</v>
       </c>
@@ -3217,22 +3189,22 @@
         <v>21848.15</v>
       </c>
       <c r="C52">
-        <v>158.87799999999999</v>
+        <v>158.878</v>
       </c>
       <c r="E52">
-        <v>0.25700000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="F52">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="G52">
-        <v>0.69099999999999995</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H52">
         <v>13124.6</v>
       </c>
       <c r="I52">
-        <v>153.63399999999999</v>
+        <v>153.634</v>
       </c>
       <c r="K52">
         <v>0.251</v>
@@ -3253,13 +3225,13 @@
         <v>6738.29</v>
       </c>
       <c r="U52">
-        <v>164.12200000000001</v>
+        <v>164.122</v>
       </c>
       <c r="W52">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="X52">
-        <v>0.30099999999999999</v>
+        <v>0.301</v>
       </c>
       <c r="Y52">
         <v>1.978</v>

--- a/Indicator_4/Real_data/Blue_Shark_NAtl.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_NAtl.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
+    <sheet name="B_BMSY" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>337.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -498,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>337.3</t>
+          <t>0.576</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3240,4 +3241,694 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StDev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSB_1971</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2.250185001233342</v>
+      </c>
+      <c r="C2">
+        <v>0.2578980526536844</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSB_1972</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2.256908379389196</v>
+      </c>
+      <c r="C3">
+        <v>0.2578100520670138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSB_1973</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2.26230508203388</v>
+      </c>
+      <c r="C4">
+        <v>0.2575300502003347</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSB_1974</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2.266701778011853</v>
+      </c>
+      <c r="C5">
+        <v>0.257112380749205</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSB_1975</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2.267078447189648</v>
+      </c>
+      <c r="C6">
+        <v>0.2558423722824819</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSB_1976</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2.255438369589131</v>
+      </c>
+      <c r="C7">
+        <v>0.2525076833845559</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSB_1977</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2.283738558257055</v>
+      </c>
+      <c r="C8">
+        <v>0.241409609397396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSB_1978</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2.309038726924846</v>
+      </c>
+      <c r="C9">
+        <v>0.2215014766765112</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSB_1979</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2.326025506836713</v>
+      </c>
+      <c r="C10">
+        <v>0.2018660124400829</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSB_1980</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2.363252421682811</v>
+      </c>
+      <c r="C11">
+        <v>0.1844592297281982</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SSB_1981</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2.359559063727092</v>
+      </c>
+      <c r="C12">
+        <v>0.1704444696297975</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SSB_1982</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2.34083893892626</v>
+      </c>
+      <c r="C13">
+        <v>0.1590100600670671</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSB_1983</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2.312358749058327</v>
+      </c>
+      <c r="C14">
+        <v>0.1498419989466596</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SSB_1984</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2.256895045966973</v>
+      </c>
+      <c r="C15">
+        <v>0.1436616244108294</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SSB_1985</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2.213018086787245</v>
+      </c>
+      <c r="C16">
+        <v>0.1380175867839119</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSB_1986</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2.143334288895259</v>
+      </c>
+      <c r="C17">
+        <v>0.1340798938659591</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SSB_1987</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2.028850192334616</v>
+      </c>
+      <c r="C18">
+        <v>0.1325145500970006</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SSB_1988</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>1.875755838372256</v>
+      </c>
+      <c r="C19">
+        <v>0.1322635484236562</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SSB_1989</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>1.742294948632991</v>
+      </c>
+      <c r="C20">
+        <v>0.1303235354902366</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SSB_1990</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1.651007673384489</v>
+      </c>
+      <c r="C21">
+        <v>0.1255768371789145</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SSB_1991</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1.565660437736252</v>
+      </c>
+      <c r="C22">
+        <v>0.1212551417009447</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSB_1992</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.46658311055407</v>
+      </c>
+      <c r="C23">
+        <v>0.1179224528163521</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SSB_1993</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1.384475896505977</v>
+      </c>
+      <c r="C24">
+        <v>0.1148647657651051</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SSB_1994</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>1.281501876679178</v>
+      </c>
+      <c r="C25">
+        <v>0.1121830812205415</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSB_1995</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1.202371349142328</v>
+      </c>
+      <c r="C26">
+        <v>0.1091310608737392</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SSB_1996</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>1.096273975159834</v>
+      </c>
+      <c r="C27">
+        <v>0.1056877045846972</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SSB_1997</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>0.9884465896439311</v>
+      </c>
+      <c r="C28">
+        <v>0.1038280255201701</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SSB_1998</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>0.9247028313522091</v>
+      </c>
+      <c r="C29">
+        <v>0.1028813525423503</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSB_1999</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>0.8906526043506957</v>
+      </c>
+      <c r="C30">
+        <v>0.1023640157601051</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SSB_2000</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>0.8502690017933453</v>
+      </c>
+      <c r="C31">
+        <v>0.09988999926666177</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SSB_2001</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>0.7992819952133015</v>
+      </c>
+      <c r="C32">
+        <v>0.09902766018440123</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SSB_2002</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>0.7602617350782339</v>
+      </c>
+      <c r="C33">
+        <v>0.09823232154881033</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SSB_2003</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>0.7410082733884892</v>
+      </c>
+      <c r="C34">
+        <v>0.09640197601317342</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SSB_2004</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0.7158981059873732</v>
+      </c>
+      <c r="C35">
+        <v>0.0949779665197768</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SSB_2005</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>0.7182181214541431</v>
+      </c>
+      <c r="C36">
+        <v>0.09426929512863419</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SSB_2006</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0.7274981833212222</v>
+      </c>
+      <c r="C37">
+        <v>0.0944086293908626</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SSB_2007</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>0.7403882692551284</v>
+      </c>
+      <c r="C38">
+        <v>0.09466363109087393</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SSB_2008</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>0.7445716304775365</v>
+      </c>
+      <c r="C39">
+        <v>0.09462063080420537</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SSB_2009</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>0.7542850285668572</v>
+      </c>
+      <c r="C40">
+        <v>0.09478729858199055</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SSB_2010</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>0.7781285208568057</v>
+      </c>
+      <c r="C41">
+        <v>0.09759531730211536</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SSB_2011</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0.8187187914586098</v>
+      </c>
+      <c r="C42">
+        <v>0.1024940166267775</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SSB_2012</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>0.8659291061940413</v>
+      </c>
+      <c r="C43">
+        <v>0.1090533936892913</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SSB_2013</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0.8892392615950773</v>
+      </c>
+      <c r="C44">
+        <v>0.1135857572383816</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SSB_2014</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.8877825852172347</v>
+      </c>
+      <c r="C45">
+        <v>0.1150991006606711</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SSB_2015</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>0.9159427729518197</v>
+      </c>
+      <c r="C46">
+        <v>0.1169287795251968</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SSB_2016</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>0.9761465076433843</v>
+      </c>
+      <c r="C47">
+        <v>0.121995813305422</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SSB_2017</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1.001043340288935</v>
+      </c>
+      <c r="C48">
+        <v>0.1268378455856372</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSB_2018</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1.020480136534244</v>
+      </c>
+      <c r="C49">
+        <v>0.1309038726924846</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SSB_2019</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>1.044380295868639</v>
+      </c>
+      <c r="C50">
+        <v>0.1347582317215448</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SSB_2020</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>1.06065707104714</v>
+      </c>
+      <c r="C51">
+        <v>0.1382365882439216</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SSB_2021</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>1.054800365335769</v>
+      </c>
+      <c r="C52">
+        <v>0.1390125934172895</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>